--- a/data/Test_Data_Venituri_Cheltuieli.xlsx
+++ b/data/Test_Data_Venituri_Cheltuieli.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\!MDED\Comert exterior\COD_PAGE\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\!MDED\Comert exterior\COD_Final\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0B16CD5-A466-4AB1-91FC-5BD32A91BE68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46DE2AA4-3056-4D24-9DBC-23DF3CEC83D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Venituri" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Cheltuieli_CE" sheetId="3" r:id="rId3"/>
     <sheet name="Datoria" sheetId="5" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -179,7 +179,7 @@
     <numFmt numFmtId="164" formatCode="[$-418]mmmm\-yy;@"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -272,6 +272,12 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial Nova Cond"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -456,7 +462,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -511,24 +517,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -551,6 +542,20 @@
     <xf numFmtId="2" fontId="12" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="14" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -788,7 +793,7 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <numFmt numFmtId="165" formatCode="0.0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="[$-418]mmmm\-yy;@"/>
@@ -861,8 +866,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9A8995EA-88B0-4EC9-9C87-DBE683949867}" name="Table1" displayName="Table1" ref="A1:L105" totalsRowShown="0" headerRowDxfId="22" headerRowBorderDxfId="21" tableBorderDxfId="20">
-  <autoFilter ref="A1:L105" xr:uid="{9A8995EA-88B0-4EC9-9C87-DBE683949867}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9A8995EA-88B0-4EC9-9C87-DBE683949867}" name="Table1" displayName="Table1" ref="A1:L108" totalsRowShown="0" headerRowDxfId="22" headerRowBorderDxfId="21" tableBorderDxfId="20">
+  <autoFilter ref="A1:L108" xr:uid="{9A8995EA-88B0-4EC9-9C87-DBE683949867}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{0C77EDF9-7226-4CE7-AC3B-377E597C8A46}" name="Date" dataDxfId="19" totalsRowDxfId="18"/>
     <tableColumn id="2" xr3:uid="{C3857ACB-FDAA-4839-B0E5-6DDBA0E72643}" name="Impozit pe venitul persoanelor fizice"/>
@@ -874,9 +879,7 @@
     <tableColumn id="8" xr3:uid="{AC414890-7260-4FC1-A1BE-80352B4D68B0}" name="Contribuţii de asigurări sociale de stat obligatorii"/>
     <tableColumn id="9" xr3:uid="{CF9CE1A6-85A9-4E53-826B-C681C2B1F7FC}" name="Prime de asigurare obligatorie de asistenţă medicală"/>
     <tableColumn id="10" xr3:uid="{6D4BAE4C-7961-4C3C-A5F4-A4017AE9946D}" name="Granturi"/>
-    <tableColumn id="11" xr3:uid="{2C9C8E23-F549-45D1-9D9C-EB63077FC1C5}" name="Alte venituri" dataDxfId="17">
-      <calculatedColumnFormula>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</calculatedColumnFormula>
-    </tableColumn>
+    <tableColumn id="11" xr3:uid="{2C9C8E23-F549-45D1-9D9C-EB63077FC1C5}" name="Alte venituri" dataDxfId="17"/>
     <tableColumn id="12" xr3:uid="{7363AF1A-969A-4E2C-A3EC-1F31BBE35C33}" name="TOTAL VENITURI"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -904,8 +907,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{824147C9-B421-43FC-B498-380247088266}" name="Table3" displayName="Table3" ref="A2:K92" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
-  <autoFilter ref="A2:K92" xr:uid="{824147C9-B421-43FC-B498-380247088266}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{824147C9-B421-43FC-B498-380247088266}" name="Table3" displayName="Table3" ref="A2:K97" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+  <autoFilter ref="A2:K97" xr:uid="{824147C9-B421-43FC-B498-380247088266}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{AF448E6A-F20E-4F8C-8F95-004926FBDE60}" name="Date" dataDxfId="10"/>
     <tableColumn id="2" xr3:uid="{41C650A5-8D4A-4B4E-999B-EF5F2DC7FB32}" name="Cheltuieli de personal" dataDxfId="9"/>
@@ -1189,7 +1192,7 @@
   <sheetPr>
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:L105"/>
+  <dimension ref="A1:O110"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.140625" bestFit="1" customWidth="1"/>
@@ -1275,8 +1278,7 @@
       <c r="J2">
         <v>9</v>
       </c>
-      <c r="K2">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K2" s="5">
         <v>282.40000000000055</v>
       </c>
       <c r="L2">
@@ -1314,8 +1316,7 @@
       <c r="J3">
         <v>5</v>
       </c>
-      <c r="K3">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K3" s="5">
         <v>150.20000000000027</v>
       </c>
       <c r="L3">
@@ -1353,8 +1354,7 @@
       <c r="J4">
         <v>23.6</v>
       </c>
-      <c r="K4">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K4" s="5">
         <v>182.70000000000073</v>
       </c>
       <c r="L4">
@@ -1392,8 +1392,7 @@
       <c r="J5">
         <v>6.1999999999999957</v>
       </c>
-      <c r="K5">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K5" s="5">
         <v>310.99999999999955</v>
       </c>
       <c r="L5">
@@ -1431,8 +1430,7 @@
       <c r="J6">
         <v>26.900000000000006</v>
       </c>
-      <c r="K6">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K6" s="5">
         <v>312.59999999999809</v>
       </c>
       <c r="L6">
@@ -1470,8 +1468,7 @@
       <c r="J7">
         <v>13.599999999999994</v>
       </c>
-      <c r="K7">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K7" s="5">
         <v>409.30000000000473</v>
       </c>
       <c r="L7">
@@ -1509,8 +1506,7 @@
       <c r="J8">
         <v>53.09999999999998</v>
       </c>
-      <c r="K8">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K8" s="5">
         <v>330.69999999999209</v>
       </c>
       <c r="L8">
@@ -1548,8 +1544,7 @@
       <c r="J9">
         <v>20.900000000000034</v>
       </c>
-      <c r="K9">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K9" s="5">
         <v>283.30000000000837</v>
       </c>
       <c r="L9">
@@ -1587,8 +1582,7 @@
       <c r="J10">
         <v>12.799999999999983</v>
       </c>
-      <c r="K10">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K10" s="5">
         <v>283.099999999994</v>
       </c>
       <c r="L10">
@@ -1626,8 +1620,7 @@
       <c r="J11">
         <v>10.300000000000011</v>
       </c>
-      <c r="K11">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K11" s="5">
         <v>324.29999999999472</v>
       </c>
       <c r="L11">
@@ -1665,8 +1658,7 @@
       <c r="J12">
         <v>53.5</v>
       </c>
-      <c r="K12">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K12" s="5">
         <v>87.30000000000382</v>
       </c>
       <c r="L12">
@@ -1704,8 +1696,7 @@
       <c r="J13">
         <v>773.90000000000009</v>
       </c>
-      <c r="K13">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K13" s="5">
         <v>167.80000000000837</v>
       </c>
       <c r="L13">
@@ -1743,8 +1734,7 @@
       <c r="J14">
         <v>10.199999999999999</v>
       </c>
-      <c r="K14">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K14" s="5">
         <v>204.69999999999982</v>
       </c>
       <c r="L14">
@@ -1782,8 +1772,7 @@
       <c r="J15">
         <v>39.299999999999997</v>
       </c>
-      <c r="K15">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K15" s="5">
         <v>224.89999999999964</v>
       </c>
       <c r="L15">
@@ -1821,8 +1810,7 @@
       <c r="J16">
         <v>17.599999999999994</v>
       </c>
-      <c r="K16">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K16" s="5">
         <v>240.29999999999927</v>
       </c>
       <c r="L16">
@@ -1860,8 +1848,7 @@
       <c r="J17">
         <v>28.800000000000011</v>
       </c>
-      <c r="K17">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K17" s="5">
         <v>349.19999999999936</v>
       </c>
       <c r="L17">
@@ -1899,8 +1886,7 @@
       <c r="J18">
         <v>9.1999999999999886</v>
       </c>
-      <c r="K18">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K18" s="5">
         <v>432</v>
       </c>
       <c r="L18">
@@ -1938,8 +1924,7 @@
       <c r="J19">
         <v>20.400000000000006</v>
       </c>
-      <c r="K19">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K19" s="5">
         <v>375.30000000000382</v>
       </c>
       <c r="L19">
@@ -1977,8 +1962,7 @@
       <c r="J20">
         <v>45.5</v>
       </c>
-      <c r="K20">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K20" s="5">
         <v>365.40000000000691</v>
       </c>
       <c r="L20">
@@ -2016,8 +2000,7 @@
       <c r="J21">
         <v>3.5000000000000284</v>
       </c>
-      <c r="K21">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K21" s="5">
         <v>242.19999999998709</v>
       </c>
       <c r="L21">
@@ -2055,8 +2038,7 @@
       <c r="J22">
         <v>35.099999999999994</v>
       </c>
-      <c r="K22">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K22" s="5">
         <v>257.30000000000655</v>
       </c>
       <c r="L22">
@@ -2094,8 +2076,7 @@
       <c r="J23">
         <v>44.099999999999966</v>
       </c>
-      <c r="K23">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K23" s="5">
         <v>331.60000000000218</v>
       </c>
       <c r="L23">
@@ -2133,8 +2114,7 @@
       <c r="J24">
         <v>12.300000000000011</v>
       </c>
-      <c r="K24">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K24" s="5">
         <v>217.29999999998745</v>
       </c>
       <c r="L24">
@@ -2172,8 +2152,7 @@
       <c r="J25">
         <v>121.39999999999998</v>
       </c>
-      <c r="K25">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K25" s="5">
         <v>156.80000000002474</v>
       </c>
       <c r="L25">
@@ -2211,8 +2190,7 @@
       <c r="J26">
         <v>50.1</v>
       </c>
-      <c r="K26">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K26" s="5">
         <v>374.89999999999873</v>
       </c>
       <c r="L26">
@@ -2250,8 +2228,7 @@
       <c r="J27">
         <v>8.2999999999999972</v>
       </c>
-      <c r="K27">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K27" s="5">
         <v>221.59999999999854</v>
       </c>
       <c r="L27">
@@ -2289,8 +2266,7 @@
       <c r="J28">
         <v>20.800000000000004</v>
       </c>
-      <c r="K28">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K28" s="5">
         <v>316.70000000000346</v>
       </c>
       <c r="L28">
@@ -2328,8 +2304,7 @@
       <c r="J29">
         <v>47.099999999999994</v>
       </c>
-      <c r="K29">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K29" s="5">
         <v>361.29999999999382</v>
       </c>
       <c r="L29">
@@ -2367,8 +2342,7 @@
       <c r="J30">
         <v>18.000000000000014</v>
       </c>
-      <c r="K30">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K30" s="5">
         <v>251.50000000000364</v>
       </c>
       <c r="L30">
@@ -2406,8 +2380,7 @@
       <c r="J31">
         <v>5.0999999999999659</v>
       </c>
-      <c r="K31">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K31" s="5">
         <v>331.90000000000146</v>
       </c>
       <c r="L31">
@@ -2445,8 +2418,7 @@
       <c r="J32">
         <v>326.80000000000007</v>
       </c>
-      <c r="K32">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K32" s="5">
         <v>389.29999999999836</v>
       </c>
       <c r="L32">
@@ -2484,8 +2456,7 @@
       <c r="J33">
         <v>1.6999999999999318</v>
       </c>
-      <c r="K33">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K33" s="5">
         <v>304.60000000000673</v>
       </c>
       <c r="L33">
@@ -2523,8 +2494,7 @@
       <c r="J34">
         <v>13.699999999999989</v>
       </c>
-      <c r="K34">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K34" s="5">
         <v>241.00000000000273</v>
       </c>
       <c r="L34">
@@ -2562,8 +2532,7 @@
       <c r="J35">
         <v>350.10000000000008</v>
       </c>
-      <c r="K35">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K35" s="5">
         <v>380.29999999998108</v>
       </c>
       <c r="L35">
@@ -2601,8 +2570,7 @@
       <c r="J36">
         <v>717.40000000000009</v>
       </c>
-      <c r="K36">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K36" s="5">
         <v>276.30000000002292</v>
       </c>
       <c r="L36">
@@ -2640,8 +2608,7 @@
       <c r="J37">
         <v>43.499999999999773</v>
       </c>
-      <c r="K37">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K37" s="5">
         <v>268.29999999999109</v>
       </c>
       <c r="L37">
@@ -2679,8 +2646,7 @@
       <c r="J38">
         <v>1.7</v>
       </c>
-      <c r="K38">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K38" s="5">
         <v>393.00000000000091</v>
       </c>
       <c r="L38">
@@ -2718,8 +2684,7 @@
       <c r="J39">
         <v>29.400000000000002</v>
       </c>
-      <c r="K39">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K39" s="5">
         <v>272.99999999999909</v>
       </c>
       <c r="L39">
@@ -2757,8 +2722,7 @@
       <c r="J40">
         <v>27.099999999999994</v>
       </c>
-      <c r="K40">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K40" s="5">
         <v>120.89999999999782</v>
       </c>
       <c r="L40">
@@ -2796,8 +2760,7 @@
       <c r="J41">
         <v>5</v>
       </c>
-      <c r="K41">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K41" s="5">
         <v>256.50000000000364</v>
       </c>
       <c r="L41">
@@ -2835,8 +2798,7 @@
       <c r="J42">
         <v>31.1</v>
       </c>
-      <c r="K42">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K42" s="5">
         <v>463.70000000000073</v>
       </c>
       <c r="L42">
@@ -2874,8 +2836,7 @@
       <c r="J43">
         <v>18.799999999999997</v>
       </c>
-      <c r="K43">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K43" s="5">
         <v>407.89999999999873</v>
       </c>
       <c r="L43">
@@ -2913,8 +2874,7 @@
       <c r="J44">
         <v>8.7999999999999972</v>
       </c>
-      <c r="K44">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K44" s="5">
         <v>269.50000000000546</v>
       </c>
       <c r="L44">
@@ -2952,8 +2912,7 @@
       <c r="J45">
         <v>202.60000000000002</v>
       </c>
-      <c r="K45">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K45" s="5">
         <v>269.39999999999327</v>
       </c>
       <c r="L45">
@@ -2991,8 +2950,7 @@
       <c r="J46">
         <v>19.300000000000011</v>
       </c>
-      <c r="K46">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K46" s="5">
         <v>242.39999999999691</v>
       </c>
       <c r="L46">
@@ -3030,8 +2988,7 @@
       <c r="J47">
         <v>104.69999999999999</v>
       </c>
-      <c r="K47">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K47" s="5">
         <v>376.39999999999327</v>
       </c>
       <c r="L47">
@@ -3069,8 +3026,7 @@
       <c r="J48">
         <v>41.300000000000011</v>
       </c>
-      <c r="K48">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K48" s="5">
         <v>335.80000000000746</v>
       </c>
       <c r="L48">
@@ -3108,8 +3064,7 @@
       <c r="J49">
         <v>159.7999999999999</v>
       </c>
-      <c r="K49">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K49" s="5">
         <v>289.69999999998527</v>
       </c>
       <c r="L49">
@@ -3147,8 +3102,7 @@
       <c r="J50">
         <v>186</v>
       </c>
-      <c r="K50">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K50" s="5">
         <v>413.39999999999873</v>
       </c>
       <c r="L50">
@@ -3186,8 +3140,7 @@
       <c r="J51">
         <v>30.699999999999989</v>
       </c>
-      <c r="K51">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K51" s="5">
         <v>218.70000000000164</v>
       </c>
       <c r="L51">
@@ -3225,8 +3178,7 @@
       <c r="J52">
         <v>15.200000000000017</v>
       </c>
-      <c r="K52">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K52" s="5">
         <v>305.49999999999545</v>
       </c>
       <c r="L52">
@@ -3264,8 +3216,7 @@
       <c r="J53">
         <v>7.5</v>
       </c>
-      <c r="K53">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K53" s="5">
         <v>430.60000000000673</v>
       </c>
       <c r="L53">
@@ -3303,8 +3254,7 @@
       <c r="J54">
         <v>13.800000000000011</v>
       </c>
-      <c r="K54">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K54" s="5">
         <v>412.49999999999636</v>
       </c>
       <c r="L54">
@@ -3342,8 +3292,7 @@
       <c r="J55">
         <v>29.299999999999983</v>
       </c>
-      <c r="K55">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K55" s="5">
         <v>502.09999999999582</v>
       </c>
       <c r="L55">
@@ -3381,8 +3330,7 @@
       <c r="J56">
         <v>13.699999999999989</v>
       </c>
-      <c r="K56">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K56" s="5">
         <v>527.30000000000746</v>
       </c>
       <c r="L56">
@@ -3420,8 +3368,7 @@
       <c r="J57">
         <v>4.6000000000000227</v>
       </c>
-      <c r="K57">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K57" s="5">
         <v>307.19999999998981</v>
       </c>
       <c r="L57">
@@ -3459,8 +3406,7 @@
       <c r="J58">
         <v>14.199999999999989</v>
       </c>
-      <c r="K58">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K58" s="5">
         <v>389.70000000002346</v>
       </c>
       <c r="L58">
@@ -3498,8 +3444,7 @@
       <c r="J59">
         <v>809.3</v>
       </c>
-      <c r="K59">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K59" s="5">
         <v>835.29999999999291</v>
       </c>
       <c r="L59">
@@ -3537,8 +3482,7 @@
       <c r="J60">
         <v>30.700000000000273</v>
       </c>
-      <c r="K60">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K60" s="5">
         <v>351.59999999998945</v>
       </c>
       <c r="L60">
@@ -3576,8 +3520,7 @@
       <c r="J61">
         <v>1292.3999999999999</v>
       </c>
-      <c r="K61">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K61" s="5">
         <v>358.10000000000218</v>
       </c>
       <c r="L61">
@@ -3585,41 +3528,40 @@
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A62" s="27">
+      <c r="A62" s="26">
         <v>44562</v>
       </c>
-      <c r="B62" s="28">
+      <c r="B62" s="27">
         <v>400.6</v>
       </c>
-      <c r="C62" s="28">
+      <c r="C62" s="27">
         <v>341.09999999999997</v>
       </c>
-      <c r="D62" s="28">
+      <c r="D62" s="27">
         <v>10.200000000000001</v>
       </c>
-      <c r="E62" s="28">
+      <c r="E62" s="27">
         <v>933.5</v>
       </c>
-      <c r="F62" s="28">
+      <c r="F62" s="27">
         <v>1314.7</v>
       </c>
-      <c r="G62" s="28">
+      <c r="G62" s="27">
         <v>602.50000000000011</v>
       </c>
-      <c r="H62" s="28">
+      <c r="H62" s="27">
         <v>1311.6</v>
       </c>
-      <c r="I62" s="28">
+      <c r="I62" s="27">
         <v>480.5</v>
       </c>
-      <c r="J62" s="28">
+      <c r="J62" s="27">
         <v>4.5</v>
       </c>
       <c r="K62" s="28">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
         <v>471.69999999999891</v>
       </c>
-      <c r="L62" s="28">
+      <c r="L62" s="27">
         <v>5870.9</v>
       </c>
     </row>
@@ -3654,8 +3596,7 @@
       <c r="J63">
         <v>24.6</v>
       </c>
-      <c r="K63">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K63" s="5">
         <v>317.79999999999836</v>
       </c>
       <c r="L63">
@@ -3693,8 +3634,7 @@
       <c r="J64">
         <v>65.400000000000006</v>
       </c>
-      <c r="K64">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K64" s="5">
         <v>371.50000000000273</v>
       </c>
       <c r="L64">
@@ -3732,8 +3672,7 @@
       <c r="J65">
         <v>79.199999999999989</v>
       </c>
-      <c r="K65">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K65" s="5">
         <v>360.00000000000455</v>
       </c>
       <c r="L65">
@@ -3771,8 +3710,7 @@
       <c r="J66">
         <v>13.100000000000023</v>
       </c>
-      <c r="K66">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K66" s="5">
         <v>147.49999999999818</v>
       </c>
       <c r="L66">
@@ -3810,8 +3748,7 @@
       <c r="J67">
         <v>50.199999999999989</v>
       </c>
-      <c r="K67">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K67" s="5">
         <v>536.49999999999181</v>
       </c>
       <c r="L67">
@@ -3849,8 +3786,7 @@
       <c r="J68">
         <v>19.600000000000023</v>
       </c>
-      <c r="K68">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K68" s="5">
         <v>554.60000000001855</v>
       </c>
       <c r="L68">
@@ -3888,8 +3824,7 @@
       <c r="J69">
         <v>2018</v>
       </c>
-      <c r="K69">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K69" s="5">
         <v>285.09999999996944</v>
       </c>
       <c r="L69">
@@ -3927,8 +3862,7 @@
       <c r="J70">
         <v>68.399999999999636</v>
       </c>
-      <c r="K70">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K70" s="5">
         <v>454.40000000001692</v>
       </c>
       <c r="L70">
@@ -3966,8 +3900,7 @@
       <c r="J71">
         <v>322.20000000000027</v>
       </c>
-      <c r="K71">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K71" s="5">
         <v>590.30000000000837</v>
       </c>
       <c r="L71">
@@ -4005,8 +3938,7 @@
       <c r="J72">
         <v>912</v>
       </c>
-      <c r="K72">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K72" s="5">
         <v>364.79999999998017</v>
       </c>
       <c r="L72">
@@ -4044,8 +3976,7 @@
       <c r="J73">
         <v>962.20000000000073</v>
       </c>
-      <c r="K73">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K73" s="5">
         <v>504.30000000001928</v>
       </c>
       <c r="L73">
@@ -4053,41 +3984,40 @@
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A74" s="27">
+      <c r="A74" s="26">
         <v>44927</v>
       </c>
-      <c r="B74" s="28">
+      <c r="B74" s="27">
         <v>478.6</v>
       </c>
-      <c r="C74" s="28">
+      <c r="C74" s="27">
         <v>435.4</v>
       </c>
-      <c r="D74" s="28">
+      <c r="D74" s="27">
         <v>13.9</v>
       </c>
-      <c r="E74" s="28">
+      <c r="E74" s="27">
         <v>1124.3</v>
       </c>
-      <c r="F74" s="28">
+      <c r="F74" s="27">
         <v>2017</v>
       </c>
-      <c r="G74" s="28">
+      <c r="G74" s="27">
         <v>626.79999999999995</v>
       </c>
-      <c r="H74" s="28">
+      <c r="H74" s="27">
         <v>1503.1</v>
       </c>
-      <c r="I74" s="28">
+      <c r="I74" s="27">
         <v>595.70000000000005</v>
       </c>
-      <c r="J74" s="28">
+      <c r="J74" s="27">
         <v>13.2</v>
       </c>
       <c r="K74" s="28">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
         <v>420.79999999999927</v>
       </c>
-      <c r="L74" s="28">
+      <c r="L74" s="27">
         <v>7228.7999999999993</v>
       </c>
     </row>
@@ -4122,8 +4052,7 @@
       <c r="J75">
         <v>56.999999999999986</v>
       </c>
-      <c r="K75">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K75" s="5">
         <v>428.00000000000091</v>
       </c>
       <c r="L75">
@@ -4161,8 +4090,7 @@
       <c r="J76">
         <v>346.5</v>
       </c>
-      <c r="K76">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K76" s="5">
         <v>278.59999999999854</v>
       </c>
       <c r="L76">
@@ -4200,8 +4128,7 @@
       <c r="J77">
         <v>279.80000000000013</v>
       </c>
-      <c r="K77">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K77" s="5">
         <v>521.59999999999673</v>
       </c>
       <c r="L77">
@@ -4239,8 +4166,7 @@
       <c r="J78">
         <v>74.399999999999864</v>
       </c>
-      <c r="K78">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K78" s="5">
         <v>383.89999999999964</v>
       </c>
       <c r="L78">
@@ -4278,8 +4204,7 @@
       <c r="J79">
         <v>61.200000000000045</v>
       </c>
-      <c r="K79">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K79" s="5">
         <v>282.20000000000437</v>
       </c>
       <c r="L79">
@@ -4317,8 +4242,7 @@
       <c r="J80">
         <v>689.70000000000016</v>
       </c>
-      <c r="K80">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K80" s="5">
         <v>653.20000000001801</v>
       </c>
       <c r="L80">
@@ -4356,8 +4280,7 @@
       <c r="J81">
         <v>236.99999999999977</v>
       </c>
-      <c r="K81">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K81" s="5">
         <v>538.59999999997672</v>
       </c>
       <c r="L81">
@@ -4395,8 +4318,7 @@
       <c r="J82">
         <v>1609.8</v>
       </c>
-      <c r="K82">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K82" s="5">
         <v>452.60000000000218</v>
       </c>
       <c r="L82">
@@ -4434,8 +4356,7 @@
       <c r="J83">
         <v>473.80000000000018</v>
       </c>
-      <c r="K83">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K83" s="5">
         <v>586.70000000000528</v>
       </c>
       <c r="L83">
@@ -4473,8 +4394,7 @@
       <c r="J84">
         <v>43.900000000000091</v>
       </c>
-      <c r="K84">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K84" s="5">
         <v>430.899999999996</v>
       </c>
       <c r="L84">
@@ -4512,8 +4432,7 @@
       <c r="J85">
         <v>1460.6999999999998</v>
       </c>
-      <c r="K85">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K85" s="5">
         <v>391.59999999999854</v>
       </c>
       <c r="L85">
@@ -4521,41 +4440,40 @@
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A86" s="27">
+      <c r="A86" s="26">
         <v>45292</v>
       </c>
-      <c r="B86" s="28">
+      <c r="B86" s="27">
         <v>598.29999999999995</v>
       </c>
-      <c r="C86" s="28">
+      <c r="C86" s="27">
         <v>432.70000000000005</v>
       </c>
-      <c r="D86" s="28">
+      <c r="D86" s="27">
         <v>10.7</v>
       </c>
-      <c r="E86" s="28">
+      <c r="E86" s="27">
         <v>1304.0999999999999</v>
       </c>
-      <c r="F86" s="28">
+      <c r="F86" s="27">
         <v>1559.1</v>
       </c>
-      <c r="G86" s="28">
+      <c r="G86" s="27">
         <v>814.7</v>
       </c>
-      <c r="H86" s="28">
+      <c r="H86" s="27">
         <v>1790.6</v>
       </c>
-      <c r="I86" s="28">
+      <c r="I86" s="27">
         <v>655.4</v>
       </c>
-      <c r="J86" s="28">
+      <c r="J86" s="27">
         <v>39.300000000000004</v>
       </c>
       <c r="K86" s="28">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
         <v>392.90000000000055</v>
       </c>
-      <c r="L86" s="28">
+      <c r="L86" s="27">
         <v>7597.8000000000011</v>
       </c>
     </row>
@@ -4590,8 +4508,7 @@
       <c r="J87">
         <v>75.099999999999994</v>
       </c>
-      <c r="K87">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K87" s="5">
         <v>345.39999999999782</v>
       </c>
       <c r="L87">
@@ -4629,8 +4546,7 @@
       <c r="J88">
         <v>188.99999999999997</v>
       </c>
-      <c r="K88">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K88" s="5">
         <v>361.40000000000691</v>
       </c>
       <c r="L88">
@@ -4668,8 +4584,7 @@
       <c r="J89">
         <v>161.69999999999999</v>
       </c>
-      <c r="K89">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K89" s="5">
         <v>646.69999999999345</v>
       </c>
       <c r="L89">
@@ -4707,8 +4622,7 @@
       <c r="J90">
         <v>82.000000000000057</v>
       </c>
-      <c r="K90">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K90" s="5">
         <v>612.89999999999236</v>
       </c>
       <c r="L90">
@@ -4746,8 +4660,7 @@
       <c r="J91">
         <v>26.5</v>
       </c>
-      <c r="K91">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K91" s="5">
         <v>568.40000000000146</v>
       </c>
       <c r="L91">
@@ -4785,8 +4698,7 @@
       <c r="J92">
         <v>1145</v>
       </c>
-      <c r="K92">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K92" s="5">
         <v>641.00000000001819</v>
       </c>
       <c r="L92">
@@ -4824,8 +4736,7 @@
       <c r="J93">
         <v>53.799999999999955</v>
       </c>
-      <c r="K93">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K93" s="5">
         <v>481.09999999997308</v>
       </c>
       <c r="L93">
@@ -4863,8 +4774,7 @@
       <c r="J94">
         <v>342.70000000000005</v>
       </c>
-      <c r="K94">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K94" s="5">
         <v>421.90000000001783</v>
       </c>
       <c r="L94">
@@ -4902,8 +4812,7 @@
       <c r="J95">
         <v>63.300000000000182</v>
       </c>
-      <c r="K95">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K95" s="5">
         <v>629.40000000000146</v>
       </c>
       <c r="L95">
@@ -4941,15 +4850,14 @@
       <c r="J96">
         <v>93.400000000000091</v>
       </c>
-      <c r="K96">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K96" s="5">
         <v>523.49999999997635</v>
       </c>
       <c r="L96">
         <v>8797.0999999999767</v>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>45627</v>
       </c>
@@ -4980,325 +4888,433 @@
       <c r="J97">
         <v>320.5</v>
       </c>
-      <c r="K97">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K97" s="5">
         <v>419.60000000000582</v>
       </c>
       <c r="L97">
         <v>11203.100000000006</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A98" s="27">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A98" s="26">
         <v>45658</v>
       </c>
-      <c r="B98" s="29">
+      <c r="B98" s="47">
         <v>688.3</v>
       </c>
-      <c r="C98" s="29">
+      <c r="C98" s="47">
         <v>502</v>
       </c>
-      <c r="D98" s="29">
+      <c r="D98" s="47">
         <v>8.1</v>
       </c>
-      <c r="E98" s="29">
+      <c r="E98" s="47">
         <v>1486.4</v>
       </c>
-      <c r="F98" s="29">
+      <c r="F98" s="47">
         <v>1770.7</v>
       </c>
-      <c r="G98" s="29">
+      <c r="G98" s="47">
         <v>962.5</v>
       </c>
-      <c r="H98" s="29">
+      <c r="H98" s="47">
         <v>2086.1</v>
       </c>
-      <c r="I98" s="29">
+      <c r="I98" s="47">
         <v>804.2</v>
       </c>
-      <c r="J98" s="29">
+      <c r="J98" s="47">
         <v>35.5</v>
       </c>
-      <c r="K98" s="29">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K98" s="47">
         <v>589.99999999999818</v>
       </c>
-      <c r="L98" s="29">
+      <c r="L98" s="47">
         <v>8933.7999999999993</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>45689</v>
       </c>
-      <c r="B99" s="4">
+      <c r="B99" s="48">
         <v>748.4</v>
       </c>
-      <c r="C99" s="4">
+      <c r="C99" s="48">
         <v>392.5</v>
       </c>
-      <c r="D99" s="4">
+      <c r="D99" s="48">
         <v>14.5</v>
       </c>
-      <c r="E99" s="4">
+      <c r="E99" s="48">
         <v>1074.2</v>
       </c>
-      <c r="F99" s="5">
+      <c r="F99" s="48">
         <v>2072.6999999999998</v>
       </c>
-      <c r="G99" s="5">
+      <c r="G99" s="48">
         <v>798.4</v>
       </c>
-      <c r="H99" s="5">
+      <c r="H99" s="48">
         <v>2132.9</v>
       </c>
-      <c r="I99" s="5">
+      <c r="I99" s="48">
         <v>785.7</v>
       </c>
-      <c r="J99" s="5">
+      <c r="J99" s="48">
         <v>12.5</v>
       </c>
-      <c r="K99" s="5">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K99" s="48">
         <v>636.69999999999982</v>
       </c>
-      <c r="L99" s="5">
+      <c r="L99" s="48">
         <v>8668.5</v>
       </c>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>45717</v>
       </c>
-      <c r="B100" s="4">
+      <c r="B100" s="48">
         <v>857.39999999999986</v>
       </c>
-      <c r="C100" s="4">
+      <c r="C100" s="48">
         <v>2094</v>
       </c>
-      <c r="D100" s="4">
+      <c r="D100" s="48">
         <v>18.999999999999996</v>
       </c>
-      <c r="E100" s="4">
+      <c r="E100" s="48">
         <v>977.59999999999991</v>
       </c>
-      <c r="F100" s="5">
+      <c r="F100" s="48">
         <v>2351.3000000000002</v>
       </c>
-      <c r="G100" s="5">
+      <c r="G100" s="48">
         <v>796.09999999999991</v>
       </c>
-      <c r="H100" s="5">
+      <c r="H100" s="48">
         <v>2189.3999999999996</v>
       </c>
-      <c r="I100" s="5">
+      <c r="I100" s="48">
         <v>894.90000000000009</v>
       </c>
-      <c r="J100" s="5">
+      <c r="J100" s="48">
         <v>943.7</v>
       </c>
-      <c r="K100">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K100" s="48">
         <v>425.79999999999745</v>
       </c>
-      <c r="L100" s="5">
+      <c r="L100" s="48">
         <v>11549.199999999997</v>
       </c>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>45748</v>
       </c>
-      <c r="B101" s="4">
+      <c r="B101" s="48">
         <v>994.29999999999973</v>
       </c>
-      <c r="C101">
+      <c r="C101" s="48">
         <v>503.19999999999982</v>
       </c>
-      <c r="D101">
+      <c r="D101" s="48">
         <v>19.700000000000003</v>
       </c>
-      <c r="E101">
+      <c r="E101" s="48">
         <v>1037.1000000000004</v>
       </c>
-      <c r="F101">
+      <c r="F101" s="48">
         <v>2252.7999999999993</v>
       </c>
-      <c r="G101">
+      <c r="G101" s="48">
         <v>887.09999999999991</v>
       </c>
-      <c r="H101">
+      <c r="H101" s="48">
         <v>2248.3000000000011</v>
       </c>
-      <c r="I101">
+      <c r="I101" s="48">
         <v>768.89999999999964</v>
       </c>
-      <c r="J101" s="5">
+      <c r="J101" s="48">
         <v>796</v>
       </c>
-      <c r="K101">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K101" s="48">
         <v>721.90000000000327</v>
       </c>
-      <c r="L101">
+      <c r="L101" s="48">
         <v>10229.300000000003</v>
       </c>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>45778</v>
       </c>
-      <c r="B102" s="4">
+      <c r="B102" s="48">
         <v>768.60000000000036</v>
       </c>
-      <c r="C102" s="4">
+      <c r="C102" s="48">
         <v>397.80000000000018</v>
       </c>
-      <c r="D102" s="4">
+      <c r="D102" s="48">
         <v>41.599999999999994</v>
       </c>
-      <c r="E102" s="4">
+      <c r="E102" s="48">
         <v>1096.1999999999998</v>
       </c>
-      <c r="F102" s="4">
+      <c r="F102" s="48">
         <v>2307.9000000000015</v>
       </c>
-      <c r="G102" s="5">
+      <c r="G102" s="48">
         <v>1038.4000000000001</v>
       </c>
-      <c r="H102" s="4">
+      <c r="H102" s="48">
         <v>2307.8999999999996</v>
       </c>
-      <c r="I102" s="4">
+      <c r="I102" s="48">
         <v>788.20000000000027</v>
       </c>
-      <c r="J102" s="4">
+      <c r="J102" s="48">
         <v>14.199999999999818</v>
       </c>
-      <c r="K102">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K102" s="48">
         <v>526.80000000000291</v>
       </c>
-      <c r="L102">
+      <c r="L102" s="48">
         <v>9287.6000000000058</v>
       </c>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>45809</v>
       </c>
-      <c r="B103" s="4">
+      <c r="B103" s="48">
         <v>897.9</v>
       </c>
-      <c r="C103" s="4">
+      <c r="C103" s="48">
         <v>1092.4000000000001</v>
       </c>
-      <c r="D103" s="4">
+      <c r="D103" s="48">
         <v>244.2</v>
       </c>
-      <c r="E103" s="4">
+      <c r="E103" s="48">
         <v>1154.8</v>
       </c>
-      <c r="F103" s="4">
+      <c r="F103" s="48">
         <v>2163.1999999999998</v>
       </c>
-      <c r="G103" s="5">
+      <c r="G103" s="48">
         <v>952.5</v>
       </c>
-      <c r="H103" s="4">
+      <c r="H103" s="48">
         <v>2586.3000000000002</v>
       </c>
-      <c r="I103" s="4">
+      <c r="I103" s="48">
         <v>868</v>
       </c>
-      <c r="J103" s="4">
+      <c r="J103" s="48">
         <v>1029.9000000000001</v>
       </c>
-      <c r="K103">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K103" s="48">
         <v>873.90000000000146</v>
       </c>
-      <c r="L103">
+      <c r="L103" s="48">
         <v>11863.1</v>
       </c>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>45839</v>
       </c>
-      <c r="B104" s="4">
+      <c r="B104" s="48">
         <v>830</v>
       </c>
-      <c r="C104" s="4">
+      <c r="C104" s="48">
         <v>491.90000000000055</v>
       </c>
-      <c r="D104" s="4">
+      <c r="D104" s="48">
         <v>90.199999999999989</v>
       </c>
-      <c r="E104" s="4">
+      <c r="E104" s="48">
         <v>1331.5999999999995</v>
       </c>
-      <c r="F104" s="4">
+      <c r="F104" s="48">
         <v>2369.3000000000011</v>
       </c>
-      <c r="G104" s="5">
+      <c r="G104" s="48">
         <v>1140.2999999999993</v>
       </c>
-      <c r="H104" s="4">
+      <c r="H104" s="48">
         <v>2439.1000000000004</v>
       </c>
-      <c r="I104" s="4">
+      <c r="I104" s="48">
         <v>823.30000000000018</v>
       </c>
-      <c r="J104" s="4">
+      <c r="J104" s="48">
         <v>923.69999999999982</v>
       </c>
-      <c r="K104">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K104" s="48">
         <v>1003.0999999999913</v>
       </c>
-      <c r="L104">
+      <c r="L104" s="48">
         <v>11442.499999999993</v>
       </c>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>45870</v>
       </c>
-      <c r="B105" s="4">
+      <c r="B105" s="48">
         <v>738.10000000000036</v>
       </c>
-      <c r="C105" s="4">
+      <c r="C105" s="48">
         <v>430.5</v>
       </c>
-      <c r="D105" s="4">
+      <c r="D105" s="48">
         <v>40.699999999999989</v>
       </c>
-      <c r="E105" s="4">
+      <c r="E105" s="48">
         <v>1278.5000000000018</v>
       </c>
-      <c r="F105" s="4">
+      <c r="F105" s="48">
         <v>2297.0999999999985</v>
       </c>
-      <c r="G105" s="5">
+      <c r="G105" s="48">
         <v>1189.9000000000015</v>
       </c>
-      <c r="H105" s="4">
+      <c r="H105" s="48">
         <v>2196</v>
       </c>
-      <c r="I105" s="4">
+      <c r="I105" s="48">
         <v>754.19999999999982</v>
       </c>
-      <c r="J105" s="4">
+      <c r="J105" s="48">
         <v>457.30000000000018</v>
       </c>
-      <c r="K105">
-        <f>Table1[[#This Row],[TOTAL VENITURI]]-SUM(Table1[[#This Row],[Impozit pe venitul persoanelor fizice]:[Granturi]])</f>
+      <c r="K105" s="48">
         <v>693.11999999999534</v>
       </c>
-      <c r="L105" s="5">
+      <c r="L105" s="48">
         <v>10075.419999999998</v>
       </c>
+    </row>
+    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A106" s="1">
+        <v>45901</v>
+      </c>
+      <c r="B106" s="48">
+        <v>759.1</v>
+      </c>
+      <c r="C106" s="48">
+        <v>1198.7</v>
+      </c>
+      <c r="D106" s="48">
+        <v>277.5</v>
+      </c>
+      <c r="E106" s="48">
+        <v>1497.4</v>
+      </c>
+      <c r="F106" s="48">
+        <v>2382.8000000000002</v>
+      </c>
+      <c r="G106" s="48">
+        <v>1204.7</v>
+      </c>
+      <c r="H106" s="48">
+        <v>2253.1</v>
+      </c>
+      <c r="I106" s="48">
+        <v>770.9</v>
+      </c>
+      <c r="J106" s="48">
+        <v>95.1</v>
+      </c>
+      <c r="K106" s="48">
+        <v>440.68000000002576</v>
+      </c>
+      <c r="L106" s="48">
+        <v>10879.980000000025</v>
+      </c>
+    </row>
+    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A107" s="1">
+        <v>45931</v>
+      </c>
+      <c r="B107" s="48">
+        <v>811.10000000000036</v>
+      </c>
+      <c r="C107" s="48">
+        <v>520.10000000000036</v>
+      </c>
+      <c r="D107" s="48">
+        <v>59</v>
+      </c>
+      <c r="E107" s="48">
+        <v>1396.2999999999993</v>
+      </c>
+      <c r="F107" s="48">
+        <v>2439.2999999999993</v>
+      </c>
+      <c r="G107" s="48">
+        <v>1072.1999999999971</v>
+      </c>
+      <c r="H107" s="48">
+        <v>2376.4000000000015</v>
+      </c>
+      <c r="I107" s="48">
+        <v>817.80000000000109</v>
+      </c>
+      <c r="J107" s="48">
+        <v>204.09999999999945</v>
+      </c>
+      <c r="K107" s="48">
+        <v>402.0999999999658</v>
+      </c>
+      <c r="L107" s="48">
+        <v>10098.399999999965</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A108" s="1">
+        <v>45962</v>
+      </c>
+      <c r="B108" s="48">
+        <v>784.69999999999891</v>
+      </c>
+      <c r="C108" s="48">
+        <v>440.69999999999982</v>
+      </c>
+      <c r="D108" s="48">
+        <v>29.399999999999977</v>
+      </c>
+      <c r="E108" s="48">
+        <v>1374.0999999999985</v>
+      </c>
+      <c r="F108" s="48">
+        <v>2326.1000000000022</v>
+      </c>
+      <c r="G108" s="48">
+        <v>1244</v>
+      </c>
+      <c r="H108" s="48">
+        <v>2335.2000000000007</v>
+      </c>
+      <c r="I108" s="48">
+        <v>787.69999999999891</v>
+      </c>
+      <c r="J108" s="48">
+        <v>63</v>
+      </c>
+      <c r="K108" s="48">
+        <v>541.0000000000382</v>
+      </c>
+      <c r="L108" s="48">
+        <v>9925.9000000000378</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O110" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
@@ -5314,7 +5330,7 @@
   <sheetPr>
     <tabColor theme="5" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:N106"/>
+  <dimension ref="A1:N108"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.140625" bestFit="1" customWidth="1"/>
@@ -7886,45 +7902,45 @@
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A62" s="27">
+      <c r="A62" s="26">
         <v>44562</v>
       </c>
-      <c r="B62" s="28">
+      <c r="B62" s="27">
         <v>256.60000000000002</v>
       </c>
-      <c r="C62" s="28">
+      <c r="C62" s="27">
         <v>43.300000000000004</v>
       </c>
-      <c r="D62" s="28">
+      <c r="D62" s="27">
         <v>375.2</v>
       </c>
-      <c r="E62" s="28">
+      <c r="E62" s="27">
         <v>159.9</v>
       </c>
-      <c r="F62" s="28">
+      <c r="F62" s="27">
         <v>13</v>
       </c>
-      <c r="G62" s="28">
+      <c r="G62" s="27">
         <v>36.200000000000003</v>
       </c>
-      <c r="H62" s="28">
+      <c r="H62" s="27">
         <v>983.1</v>
       </c>
-      <c r="I62" s="28">
+      <c r="I62" s="27">
         <v>100.3</v>
       </c>
-      <c r="J62" s="28">
+      <c r="J62" s="27">
         <v>807.3</v>
       </c>
-      <c r="K62" s="28">
+      <c r="K62" s="27">
         <v>3315.1000000000004</v>
       </c>
-      <c r="L62" s="28"/>
-      <c r="M62" s="28">
+      <c r="L62" s="27"/>
+      <c r="M62" s="27">
         <f>SUM(Table2[[#This Row],[Servicii de stat cu destinație generală]:[Protecție socială]])-L62</f>
         <v>6090</v>
       </c>
-      <c r="N62" s="28">
+      <c r="N62" s="27">
         <v>6090.0000000000009</v>
       </c>
     </row>
@@ -8394,45 +8410,45 @@
       </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A74" s="27">
+      <c r="A74" s="26">
         <v>44927</v>
       </c>
-      <c r="B74" s="28">
+      <c r="B74" s="27">
         <v>579.49999999999989</v>
       </c>
-      <c r="C74" s="28">
+      <c r="C74" s="27">
         <v>45.699999999999996</v>
       </c>
-      <c r="D74" s="28">
+      <c r="D74" s="27">
         <v>361</v>
       </c>
-      <c r="E74" s="28">
+      <c r="E74" s="27">
         <v>291.89999999999998</v>
       </c>
-      <c r="F74" s="28">
+      <c r="F74" s="27">
         <v>12.799999999999999</v>
       </c>
-      <c r="G74" s="28">
+      <c r="G74" s="27">
         <v>94.4</v>
       </c>
-      <c r="H74" s="28">
+      <c r="H74" s="27">
         <v>1062.5</v>
       </c>
-      <c r="I74" s="28">
+      <c r="I74" s="27">
         <v>150.19999999999999</v>
       </c>
-      <c r="J74" s="28">
+      <c r="J74" s="27">
         <v>880.1</v>
       </c>
-      <c r="K74" s="28">
+      <c r="K74" s="27">
         <v>3863.4999999999995</v>
       </c>
-      <c r="L74" s="28"/>
-      <c r="M74" s="28">
+      <c r="L74" s="27"/>
+      <c r="M74" s="27">
         <f>SUM(Table2[[#This Row],[Servicii de stat cu destinație generală]:[Protecție socială]])-L74</f>
         <v>7341.5999999999995</v>
       </c>
-      <c r="N74" s="28">
+      <c r="N74" s="27">
         <v>7341.6000000000022</v>
       </c>
     </row>
@@ -8914,45 +8930,45 @@
       </c>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A86" s="27">
+      <c r="A86" s="26">
         <v>45292</v>
       </c>
-      <c r="B86" s="28">
+      <c r="B86" s="27">
         <v>667.1</v>
       </c>
-      <c r="C86" s="28">
+      <c r="C86" s="27">
         <v>54.599999999999994</v>
       </c>
-      <c r="D86" s="28">
+      <c r="D86" s="27">
         <v>445.7</v>
       </c>
-      <c r="E86" s="28">
+      <c r="E86" s="27">
         <v>387.2</v>
       </c>
-      <c r="F86" s="28">
+      <c r="F86" s="27">
         <v>17.899999999999999</v>
       </c>
-      <c r="G86" s="28">
+      <c r="G86" s="27">
         <v>73.399999999999991</v>
       </c>
-      <c r="H86" s="28">
+      <c r="H86" s="27">
         <v>1088.8999999999999</v>
       </c>
-      <c r="I86" s="28">
+      <c r="I86" s="27">
         <v>152</v>
       </c>
-      <c r="J86" s="28">
+      <c r="J86" s="27">
         <v>999.30000000000007</v>
       </c>
-      <c r="K86" s="28">
+      <c r="K86" s="27">
         <v>3784.2</v>
       </c>
-      <c r="L86" s="28"/>
-      <c r="M86" s="28">
+      <c r="L86" s="27"/>
+      <c r="M86" s="27">
         <f>SUM(Table2[[#This Row],[Servicii de stat cu destinație generală]:[Protecție socială]])-L86</f>
         <v>7670.3</v>
       </c>
-      <c r="N86" s="28">
+      <c r="N86" s="27">
         <v>7670.2999999999993</v>
       </c>
     </row>
@@ -9429,45 +9445,45 @@
       </c>
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A98" s="27">
+      <c r="A98" s="26">
         <v>45658</v>
       </c>
-      <c r="B98" s="28">
+      <c r="B98" s="27">
         <v>713.1</v>
       </c>
-      <c r="C98" s="28">
+      <c r="C98" s="27">
         <v>51.1</v>
       </c>
-      <c r="D98" s="28">
+      <c r="D98" s="27">
         <v>594.4</v>
       </c>
-      <c r="E98" s="28">
+      <c r="E98" s="27">
         <v>587.29999999999995</v>
       </c>
-      <c r="F98" s="28">
+      <c r="F98" s="27">
         <v>17.100000000000001</v>
       </c>
-      <c r="G98" s="28">
+      <c r="G98" s="27">
         <v>79</v>
       </c>
-      <c r="H98" s="28">
+      <c r="H98" s="27">
         <v>1545.1</v>
       </c>
-      <c r="I98" s="28">
+      <c r="I98" s="27">
         <v>169</v>
       </c>
-      <c r="J98" s="28">
+      <c r="J98" s="27">
         <v>1145.8</v>
       </c>
-      <c r="K98" s="28">
+      <c r="K98" s="27">
         <v>4227</v>
       </c>
-      <c r="L98" s="28"/>
-      <c r="M98" s="28">
+      <c r="L98" s="27"/>
+      <c r="M98" s="27">
         <f>SUM(Table2[[#This Row],[Servicii de stat cu destinație generală]:[Protecție socială]])-L98</f>
         <v>9128.9</v>
       </c>
-      <c r="N98" s="28">
+      <c r="N98" s="27">
         <v>9128.9</v>
       </c>
     </row>
@@ -9776,16 +9792,136 @@
       </c>
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B106" s="5"/>
-      <c r="C106" s="5"/>
-      <c r="D106" s="5"/>
-      <c r="E106" s="5"/>
-      <c r="F106" s="5"/>
-      <c r="G106" s="5"/>
-      <c r="H106" s="5"/>
-      <c r="I106" s="5"/>
-      <c r="J106" s="5"/>
-      <c r="K106" s="5"/>
+      <c r="A106" s="6">
+        <v>45901</v>
+      </c>
+      <c r="B106" s="5">
+        <v>891.50000000000364</v>
+      </c>
+      <c r="C106" s="5">
+        <v>231.30000000000007</v>
+      </c>
+      <c r="D106" s="5">
+        <v>648.39999999999964</v>
+      </c>
+      <c r="E106" s="5">
+        <v>940.80000000000018</v>
+      </c>
+      <c r="F106" s="5">
+        <v>43</v>
+      </c>
+      <c r="G106" s="5">
+        <v>347.89999999999964</v>
+      </c>
+      <c r="H106" s="5">
+        <v>1502.7999999999975</v>
+      </c>
+      <c r="I106" s="5">
+        <v>272.79999999999973</v>
+      </c>
+      <c r="J106" s="5">
+        <v>1257.1000000000004</v>
+      </c>
+      <c r="K106" s="5">
+        <v>4584.8000000000102</v>
+      </c>
+      <c r="L106">
+        <v>2</v>
+      </c>
+      <c r="M106">
+        <v>10718.400000000011</v>
+      </c>
+      <c r="N106">
+        <v>10718.400000000011</v>
+      </c>
+    </row>
+    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A107" s="6">
+        <v>45931</v>
+      </c>
+      <c r="B107">
+        <v>1232.4999999999991</v>
+      </c>
+      <c r="C107">
+        <v>123.70000000000005</v>
+      </c>
+      <c r="D107">
+        <v>816.80000000000018</v>
+      </c>
+      <c r="E107">
+        <v>1118.8999999999996</v>
+      </c>
+      <c r="F107">
+        <v>46.300000000000011</v>
+      </c>
+      <c r="G107">
+        <v>485.30000000000018</v>
+      </c>
+      <c r="H107">
+        <v>1396.1000000000004</v>
+      </c>
+      <c r="I107">
+        <v>320.19999999999982</v>
+      </c>
+      <c r="J107">
+        <v>1953.0999999999985</v>
+      </c>
+      <c r="K107">
+        <v>4292.1999999999971</v>
+      </c>
+      <c r="L107">
+        <v>2</v>
+      </c>
+      <c r="M107">
+        <v>11783.099999999995</v>
+      </c>
+      <c r="N107">
+        <v>11783.099999999995</v>
+      </c>
+    </row>
+    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A108" s="6">
+        <v>45962</v>
+      </c>
+      <c r="B108">
+        <v>1064.7000000000007</v>
+      </c>
+      <c r="C108">
+        <v>170.59999999999991</v>
+      </c>
+      <c r="D108">
+        <v>695.10000000000036</v>
+      </c>
+      <c r="E108">
+        <v>1300.2999999999993</v>
+      </c>
+      <c r="F108">
+        <v>32.5</v>
+      </c>
+      <c r="G108">
+        <v>384.80000000000018</v>
+      </c>
+      <c r="H108">
+        <v>1997.600000000004</v>
+      </c>
+      <c r="I108">
+        <v>248.30000000000064</v>
+      </c>
+      <c r="J108">
+        <v>1837.5</v>
+      </c>
+      <c r="K108">
+        <v>4150.6000000000058</v>
+      </c>
+      <c r="L108">
+        <v>2</v>
+      </c>
+      <c r="M108">
+        <v>11880.000000000011</v>
+      </c>
+      <c r="N108">
+        <v>11880.000000000011</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9804,7 +9940,7 @@
   <sheetPr>
     <tabColor theme="5" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:L92"/>
+  <dimension ref="A1:L97"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.140625" bestFit="1" customWidth="1"/>
@@ -9816,20 +9952,20 @@
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="17"/>
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="33" t="s">
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="33"/>
-      <c r="K1" s="33"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
     </row>
     <row r="2" spans="1:12" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
@@ -13220,10 +13356,10 @@
       <c r="B91" s="9">
         <v>2506.1999999999989</v>
       </c>
-      <c r="C91" s="2">
+      <c r="C91" s="9">
         <v>2177.7999999999993</v>
       </c>
-      <c r="D91" s="2">
+      <c r="D91" s="9">
         <v>435.10000000000014</v>
       </c>
       <c r="E91" s="9">
@@ -13232,19 +13368,19 @@
       <c r="F91" s="9">
         <v>375.99999999999977</v>
       </c>
-      <c r="G91" s="2">
+      <c r="G91" s="9">
         <v>4478.4000000000051</v>
       </c>
-      <c r="H91" s="2">
+      <c r="H91" s="9">
         <v>410.5</v>
       </c>
       <c r="I91" s="9">
         <v>451</v>
       </c>
-      <c r="J91" s="2">
+      <c r="J91" s="9">
         <v>259.90000000000009</v>
       </c>
-      <c r="K91" s="2">
+      <c r="K91" s="9">
         <v>-45.5</v>
       </c>
       <c r="L91">
@@ -13264,10 +13400,10 @@
       <c r="D92" s="2">
         <v>263.2</v>
       </c>
-      <c r="E92" s="2">
+      <c r="E92" s="9">
         <v>376.8</v>
       </c>
-      <c r="F92" s="26">
+      <c r="F92" s="10">
         <v>400.1</v>
       </c>
       <c r="G92" s="2">
@@ -13287,6 +13423,196 @@
       </c>
       <c r="L92">
         <v>11994.8</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A93" s="3">
+        <v>45839</v>
+      </c>
+      <c r="B93" s="9">
+        <v>2533.1000000000004</v>
+      </c>
+      <c r="C93" s="2">
+        <v>1655.2999999999993</v>
+      </c>
+      <c r="D93" s="2">
+        <v>346.19999999999982</v>
+      </c>
+      <c r="E93" s="2">
+        <v>310.39999999999964</v>
+      </c>
+      <c r="F93" s="9">
+        <v>503</v>
+      </c>
+      <c r="G93" s="2">
+        <v>4132.3999999999978</v>
+      </c>
+      <c r="H93" s="2">
+        <v>363.20000000000027</v>
+      </c>
+      <c r="I93" s="2">
+        <v>636</v>
+      </c>
+      <c r="J93" s="2">
+        <v>187.90000000000009</v>
+      </c>
+      <c r="K93" s="2">
+        <v>-41.300000000000011</v>
+      </c>
+      <c r="L93">
+        <v>10626.199999999999</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A94" s="3">
+        <v>45870</v>
+      </c>
+      <c r="B94" s="9">
+        <v>1969.6999999999971</v>
+      </c>
+      <c r="C94" s="9">
+        <v>2358</v>
+      </c>
+      <c r="D94" s="2">
+        <v>345.40000000000055</v>
+      </c>
+      <c r="E94" s="2">
+        <v>244.90000000000009</v>
+      </c>
+      <c r="F94" s="9">
+        <v>626</v>
+      </c>
+      <c r="G94" s="2">
+        <v>4115.9999999999964</v>
+      </c>
+      <c r="H94" s="2">
+        <v>206.59999999999945</v>
+      </c>
+      <c r="I94" s="2">
+        <v>780.69999999999982</v>
+      </c>
+      <c r="J94" s="2">
+        <v>177.59999999999991</v>
+      </c>
+      <c r="K94" s="2">
+        <v>-61.599999999999994</v>
+      </c>
+      <c r="L94">
+        <v>10763.299999999996</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A95" s="3">
+        <v>45901</v>
+      </c>
+      <c r="B95" s="9">
+        <v>2085.7000000000044</v>
+      </c>
+      <c r="C95" s="9">
+        <v>1887.0999999999985</v>
+      </c>
+      <c r="D95" s="9">
+        <v>254.39999999999964</v>
+      </c>
+      <c r="E95" s="9">
+        <v>293.70000000000027</v>
+      </c>
+      <c r="F95" s="9">
+        <v>359.69999999999982</v>
+      </c>
+      <c r="G95" s="9">
+        <v>4352.8000000000029</v>
+      </c>
+      <c r="H95" s="9">
+        <v>377.20000000000027</v>
+      </c>
+      <c r="I95" s="9">
+        <v>879.30000000000018</v>
+      </c>
+      <c r="J95" s="9">
+        <v>272.49999999999977</v>
+      </c>
+      <c r="K95" s="9">
+        <v>-42.300000000000011</v>
+      </c>
+      <c r="L95">
+        <v>10720.100000000006</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A96" s="3">
+        <v>45931</v>
+      </c>
+      <c r="B96" s="9">
+        <v>2511.8999999999978</v>
+      </c>
+      <c r="C96" s="2">
+        <v>1806.4000000000015</v>
+      </c>
+      <c r="D96" s="2">
+        <v>620.90000000000009</v>
+      </c>
+      <c r="E96" s="9">
+        <v>271.59999999999945</v>
+      </c>
+      <c r="F96" s="10">
+        <v>592.80000000000018</v>
+      </c>
+      <c r="G96" s="2">
+        <v>4211.5000000000073</v>
+      </c>
+      <c r="H96" s="2">
+        <v>358.49999999999955</v>
+      </c>
+      <c r="I96" s="2">
+        <v>1097.5</v>
+      </c>
+      <c r="J96" s="2">
+        <v>331.80000000000041</v>
+      </c>
+      <c r="K96" s="2">
+        <v>-17.799999999999955</v>
+      </c>
+      <c r="L96">
+        <v>11785.100000000008</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A97" s="3">
+        <v>45962</v>
+      </c>
+      <c r="B97" s="9">
+        <v>2468.2999999999993</v>
+      </c>
+      <c r="C97" s="2">
+        <v>2530.5</v>
+      </c>
+      <c r="D97" s="2">
+        <v>495.29999999999973</v>
+      </c>
+      <c r="E97" s="2">
+        <v>206.80000000000018</v>
+      </c>
+      <c r="F97" s="9">
+        <v>607.69999999999982</v>
+      </c>
+      <c r="G97" s="2">
+        <v>3945</v>
+      </c>
+      <c r="H97" s="2">
+        <v>337.90000000000055</v>
+      </c>
+      <c r="I97" s="2">
+        <v>959.10000000000036</v>
+      </c>
+      <c r="J97" s="2">
+        <v>356.59999999999945</v>
+      </c>
+      <c r="K97" s="2">
+        <v>-25.199999999999989</v>
+      </c>
+      <c r="L97">
+        <v>11882</v>
       </c>
     </row>
   </sheetData>
@@ -13304,1925 +13630,1976 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDB67F21-77ED-4F3B-AFC9-34ABE2118DD9}">
-  <dimension ref="A1:F105"/>
+  <dimension ref="A1:F108"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15" style="42" customWidth="1"/>
-    <col min="2" max="2" width="10.5703125" style="42" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" style="42" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="42" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" style="42"/>
-    <col min="6" max="6" width="13.42578125" style="42" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="42"/>
+    <col min="1" max="1" width="15" style="37" customWidth="1"/>
+    <col min="2" max="2" width="10.5703125" style="37" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" style="37" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" style="37" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" style="37"/>
+    <col min="6" max="6" width="13.42578125" style="37" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="37"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="41" t="s">
+      <c r="B1" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="41" t="s">
+      <c r="C1" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="D1" s="41" t="s">
+      <c r="D1" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="41" t="s">
+      <c r="E1" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="41" t="s">
+      <c r="F1" s="36" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="43">
+      <c r="A2" s="38">
         <v>42736</v>
       </c>
-      <c r="B2" s="37">
+      <c r="B2" s="32">
         <v>21364.78</v>
       </c>
-      <c r="C2" s="37">
+      <c r="C2" s="32">
         <v>29711.838048639998</v>
       </c>
-      <c r="D2" s="51">
+      <c r="D2" s="46">
         <v>1482.674</v>
       </c>
-      <c r="E2" s="45">
+      <c r="E2" s="40">
         <v>20.039359999999999</v>
       </c>
-      <c r="F2" s="51"/>
+      <c r="F2" s="46"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="43">
+      <c r="A3" s="38">
         <v>42767</v>
       </c>
-      <c r="B3" s="34">
+      <c r="B3" s="29">
         <v>21382.240000000002</v>
       </c>
-      <c r="C3" s="34">
+      <c r="C3" s="29">
         <v>30471.696338999998</v>
       </c>
-      <c r="D3" s="51">
+      <c r="D3" s="46">
         <v>1523.6610000000001</v>
       </c>
-      <c r="E3" s="46">
+      <c r="E3" s="41">
         <v>19.998999999999999</v>
       </c>
-      <c r="F3" s="51"/>
+      <c r="F3" s="46"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="43">
+      <c r="A4" s="38">
         <v>42795</v>
       </c>
-      <c r="B4" s="34">
+      <c r="B4" s="29">
         <v>21793.439999999999</v>
       </c>
-      <c r="C4" s="34">
+      <c r="C4" s="29">
         <v>29855.757002000002</v>
       </c>
-      <c r="D4" s="51">
+      <c r="D4" s="46">
         <v>1532.66</v>
       </c>
-      <c r="E4" s="46">
+      <c r="E4" s="41">
         <v>19.479700000000001</v>
       </c>
-      <c r="F4" s="51"/>
+      <c r="F4" s="46"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="43">
+      <c r="A5" s="38">
         <v>42826</v>
       </c>
-      <c r="B5" s="34">
+      <c r="B5" s="29">
         <v>21586.43</v>
       </c>
-      <c r="C5" s="34">
+      <c r="C5" s="29">
         <v>29950.561724399999</v>
       </c>
-      <c r="D5" s="51">
+      <c r="D5" s="46">
         <v>1555.3320000000001</v>
       </c>
-      <c r="E5" s="46">
+      <c r="E5" s="41">
         <v>19.256699999999999</v>
       </c>
-      <c r="F5" s="51"/>
+      <c r="F5" s="46"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="43">
+      <c r="A6" s="38">
         <v>42856</v>
       </c>
-      <c r="B6" s="34">
+      <c r="B6" s="29">
         <v>21577.52</v>
       </c>
-      <c r="C6" s="34">
+      <c r="C6" s="29">
         <v>28838.712512499998</v>
       </c>
-      <c r="D6" s="51">
+      <c r="D6" s="46">
         <v>1582.675</v>
       </c>
-      <c r="E6" s="46">
+      <c r="E6" s="41">
         <v>18.221499999999999</v>
       </c>
-      <c r="F6" s="51"/>
+      <c r="F6" s="46"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="43">
+      <c r="A7" s="38">
         <v>42887</v>
       </c>
-      <c r="B7" s="34">
+      <c r="B7" s="29">
         <v>21526.58</v>
       </c>
-      <c r="C7" s="34">
+      <c r="C7" s="29">
         <v>29130.744017070123</v>
       </c>
-      <c r="D7" s="51">
+      <c r="D7" s="46">
         <v>1604.6106738349999</v>
       </c>
-      <c r="E7" s="46">
+      <c r="E7" s="41">
         <v>18.154399999999999</v>
       </c>
-      <c r="F7" s="51"/>
+      <c r="F7" s="46"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="43">
+      <c r="A8" s="38">
         <v>42917</v>
       </c>
-      <c r="B8" s="34">
+      <c r="B8" s="29">
         <v>21536.84</v>
       </c>
-      <c r="C8" s="34">
+      <c r="C8" s="29">
         <v>29426.445880000003</v>
       </c>
-      <c r="D8" s="51">
+      <c r="D8" s="46">
         <v>1626.04</v>
       </c>
-      <c r="E8" s="46">
+      <c r="E8" s="41">
         <v>18.097000000000001</v>
       </c>
-      <c r="F8" s="51"/>
+      <c r="F8" s="46"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="43">
+      <c r="A9" s="38">
         <v>42948</v>
       </c>
-      <c r="B9" s="34">
+      <c r="B9" s="29">
         <v>21641.627</v>
       </c>
-      <c r="C9" s="34">
+      <c r="C9" s="29">
         <v>29258.109224499996</v>
       </c>
-      <c r="D9" s="51">
+      <c r="D9" s="46">
         <v>1638.7149999999999</v>
       </c>
-      <c r="E9" s="46">
+      <c r="E9" s="41">
         <v>17.854299999999999</v>
       </c>
-      <c r="F9" s="51"/>
+      <c r="F9" s="46"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="43">
+      <c r="A10" s="38">
         <v>42979</v>
       </c>
-      <c r="B10" s="34">
+      <c r="B10" s="29">
         <v>21911.93</v>
       </c>
-      <c r="C10" s="34">
+      <c r="C10" s="29">
         <v>29297.283630342412</v>
       </c>
-      <c r="D10" s="51">
+      <c r="D10" s="46">
         <v>1663.5125303259999</v>
       </c>
-      <c r="E10" s="46">
+      <c r="E10" s="41">
         <v>17.611699999999999</v>
       </c>
-      <c r="F10" s="51"/>
+      <c r="F10" s="46"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="43">
+      <c r="A11" s="38">
         <v>43009</v>
       </c>
-      <c r="B11" s="34">
+      <c r="B11" s="29">
         <v>22153.58</v>
       </c>
-      <c r="C11" s="34">
+      <c r="C11" s="29">
         <v>28720.779971200001</v>
       </c>
-      <c r="D11" s="51">
+      <c r="D11" s="46">
         <v>1658.4159999999999</v>
       </c>
-      <c r="E11" s="46">
+      <c r="E11" s="41">
         <v>17.318200000000001</v>
       </c>
-      <c r="F11" s="51"/>
+      <c r="F11" s="46"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="43">
+      <c r="A12" s="38">
         <v>43040</v>
       </c>
-      <c r="B12" s="34">
+      <c r="B12" s="29">
         <v>22367.1</v>
       </c>
-      <c r="C12" s="34">
+      <c r="C12" s="29">
         <v>28839.243887999997</v>
       </c>
-      <c r="D12" s="51">
+      <c r="D12" s="46">
         <v>1678.32</v>
       </c>
-      <c r="E12" s="46">
+      <c r="E12" s="41">
         <v>17.183399999999999</v>
       </c>
-      <c r="F12" s="51"/>
+      <c r="F12" s="46"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="43">
+      <c r="A13" s="38">
         <v>43070</v>
       </c>
-      <c r="B13" s="39">
+      <c r="B13" s="34">
         <v>22578.53</v>
       </c>
-      <c r="C13" s="39">
+      <c r="C13" s="34">
         <v>29081.812647643445</v>
       </c>
-      <c r="D13" s="51">
+      <c r="D13" s="46">
         <v>1700.6709072199999</v>
       </c>
-      <c r="E13" s="47">
+      <c r="E13" s="42">
         <v>17.100200000000001</v>
       </c>
-      <c r="F13" s="51">
+      <c r="F13" s="46">
         <v>176007.29300000001</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="43">
+      <c r="A14" s="38">
         <v>43101</v>
       </c>
-      <c r="B14" s="36">
+      <c r="B14" s="31">
         <v>22621.15</v>
       </c>
-      <c r="C14" s="36">
+      <c r="C14" s="31">
         <v>29157.859280856766</v>
       </c>
-      <c r="D14" s="51">
+      <c r="D14" s="46">
         <v>1744.08929728</v>
       </c>
-      <c r="E14" s="48">
+      <c r="E14" s="43">
         <v>16.7181</v>
       </c>
-      <c r="F14" s="51"/>
+      <c r="F14" s="46"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="43">
+      <c r="A15" s="38">
         <v>43132</v>
       </c>
-      <c r="B15" s="35">
+      <c r="B15" s="30">
         <v>22743.632770759999</v>
       </c>
-      <c r="C15" s="35">
+      <c r="C15" s="30">
         <v>28555.611615961479</v>
       </c>
-      <c r="D15" s="51">
+      <c r="D15" s="46">
         <v>1710.53142542</v>
       </c>
-      <c r="E15" s="49">
+      <c r="E15" s="44">
         <v>16.693999999999999</v>
       </c>
-      <c r="F15" s="51"/>
+      <c r="F15" s="46"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="43">
+      <c r="A16" s="38">
         <v>43160</v>
       </c>
-      <c r="B16" s="35">
+      <c r="B16" s="30">
         <v>22826.90699996</v>
       </c>
-      <c r="C16" s="35">
+      <c r="C16" s="30">
         <v>28123.849073070276</v>
       </c>
-      <c r="D16" s="51">
+      <c r="D16" s="46">
         <v>1707.77740438</v>
       </c>
-      <c r="E16" s="49">
+      <c r="E16" s="44">
         <v>16.4681</v>
       </c>
-      <c r="F16" s="51"/>
+      <c r="F16" s="46"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="43">
+      <c r="A17" s="38">
         <v>43191</v>
       </c>
-      <c r="B17" s="35">
+      <c r="B17" s="30">
         <v>22872.6</v>
       </c>
-      <c r="C17" s="35">
+      <c r="C17" s="30">
         <v>27974.515820674496</v>
       </c>
-      <c r="D17" s="51">
+      <c r="D17" s="46">
         <v>1692.6963695300001</v>
       </c>
-      <c r="E17" s="49">
+      <c r="E17" s="44">
         <v>16.526599999999998</v>
       </c>
-      <c r="F17" s="51"/>
+      <c r="F17" s="46"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="43">
+      <c r="A18" s="38">
         <v>43221</v>
       </c>
-      <c r="B18" s="35">
+      <c r="B18" s="30">
         <v>22788.52</v>
       </c>
-      <c r="C18" s="35">
+      <c r="C18" s="30">
         <v>28047.191644831866</v>
       </c>
-      <c r="D18" s="51">
+      <c r="D18" s="46">
         <v>1654.33068957</v>
       </c>
-      <c r="E18" s="49">
+      <c r="E18" s="44">
         <v>16.953800000000001</v>
       </c>
-      <c r="F18" s="51"/>
+      <c r="F18" s="46"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="43">
+      <c r="A19" s="38">
         <v>43252</v>
       </c>
-      <c r="B19" s="35">
+      <c r="B19" s="30">
         <v>22798.32</v>
       </c>
-      <c r="C19" s="35">
+      <c r="C19" s="30">
         <v>28128.719375381686</v>
       </c>
-      <c r="D19" s="51">
+      <c r="D19" s="46">
         <v>1670.0539912950001</v>
       </c>
-      <c r="E19" s="49">
+      <c r="E19" s="44">
         <v>16.843</v>
       </c>
-      <c r="F19" s="51"/>
+      <c r="F19" s="46"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="43">
+      <c r="A20" s="38">
         <v>43282</v>
       </c>
-      <c r="B20" s="35">
+      <c r="B20" s="30">
         <v>22902.200987159998</v>
       </c>
-      <c r="C20" s="35">
+      <c r="C20" s="30">
         <v>28413.930335999998</v>
       </c>
-      <c r="D20" s="51">
+      <c r="D20" s="46">
         <v>1713.83</v>
       </c>
-      <c r="E20" s="49">
+      <c r="E20" s="44">
         <v>16.5792</v>
       </c>
-      <c r="F20" s="51"/>
+      <c r="F20" s="46"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="43">
+      <c r="A21" s="38">
         <v>43313</v>
       </c>
-      <c r="B21" s="35">
+      <c r="B21" s="30">
         <v>23087.16</v>
       </c>
-      <c r="C21" s="35">
+      <c r="C21" s="30">
         <v>28048.758837873756</v>
       </c>
-      <c r="D21" s="51">
+      <c r="D21" s="46">
         <v>1678.571316278</v>
       </c>
-      <c r="E21" s="49">
+      <c r="E21" s="44">
         <v>16.709900000000001</v>
       </c>
-      <c r="F21" s="51"/>
+      <c r="F21" s="46"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="43">
+      <c r="A22" s="38">
         <v>43344</v>
       </c>
-      <c r="B22" s="35">
+      <c r="B22" s="30">
         <v>23146.529858239999</v>
       </c>
-      <c r="C22" s="35">
+      <c r="C22" s="30">
         <v>28415.333243249625</v>
       </c>
-      <c r="D22" s="51">
+      <c r="D22" s="46">
         <v>1684.999925476</v>
       </c>
-      <c r="E22" s="49">
+      <c r="E22" s="44">
         <v>16.863700000000001</v>
       </c>
-      <c r="F22" s="51"/>
+      <c r="F22" s="46"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="43">
+      <c r="A23" s="38">
         <v>43374</v>
       </c>
-      <c r="B23" s="35">
+      <c r="B23" s="30">
         <v>22992.336903880001</v>
       </c>
-      <c r="C23" s="35">
+      <c r="C23" s="30">
         <v>28323.697985938481</v>
       </c>
-      <c r="D23" s="51">
+      <c r="D23" s="46">
         <v>1653.2048834350001</v>
       </c>
-      <c r="E23" s="49">
+      <c r="E23" s="44">
         <v>17.1326</v>
       </c>
-      <c r="F23" s="51"/>
+      <c r="F23" s="46"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="43">
+      <c r="A24" s="38">
         <v>43405</v>
       </c>
-      <c r="B24" s="35">
+      <c r="B24" s="30">
         <v>22772.84</v>
       </c>
-      <c r="C24" s="35">
+      <c r="C24" s="30">
         <v>28863.005615999999</v>
       </c>
-      <c r="D24" s="51">
+      <c r="D24" s="46">
         <v>1674.81</v>
       </c>
-      <c r="E24" s="49">
+      <c r="E24" s="44">
         <v>17.233599999999999</v>
       </c>
-      <c r="F24" s="51"/>
+      <c r="F24" s="46"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="43">
+      <c r="A25" s="38">
         <v>43435</v>
       </c>
-      <c r="B25" s="38">
+      <c r="B25" s="33">
         <v>23058.57</v>
       </c>
-      <c r="C25" s="38">
+      <c r="C25" s="33">
         <v>28954.020300000004</v>
       </c>
-      <c r="D25" s="51">
+      <c r="D25" s="46">
         <v>1689</v>
       </c>
-      <c r="E25" s="50">
+      <c r="E25" s="45">
         <v>17.142700000000001</v>
       </c>
-      <c r="F25" s="51">
+      <c r="F25" s="46">
         <v>189062.62800000003</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="43">
+      <c r="A26" s="38">
         <v>43466</v>
       </c>
-      <c r="B26" s="36">
+      <c r="B26" s="31">
         <v>23203.080916750001</v>
       </c>
-      <c r="C26" s="36">
+      <c r="C26" s="31">
         <v>29024.380564128733</v>
       </c>
-      <c r="D26" s="51">
+      <c r="D26" s="46">
         <v>1697.34212271</v>
       </c>
-      <c r="E26" s="48">
+      <c r="E26" s="43">
         <v>17.099900000000002</v>
       </c>
-      <c r="F26" s="51"/>
+      <c r="F26" s="46"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="43">
+      <c r="A27" s="38">
         <v>43497</v>
       </c>
-      <c r="B27" s="35">
+      <c r="B27" s="30">
         <v>23421.279999999999</v>
       </c>
-      <c r="C27" s="35">
+      <c r="C27" s="30">
         <v>28598.381090618703</v>
       </c>
-      <c r="D27" s="51">
+      <c r="D27" s="46">
         <v>1666.931744643</v>
       </c>
-      <c r="E27" s="49">
+      <c r="E27" s="44">
         <v>17.156300000000002</v>
       </c>
-      <c r="F27" s="51"/>
+      <c r="F27" s="46"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="43">
+      <c r="A28" s="38">
         <v>43525</v>
       </c>
-      <c r="B28" s="35">
+      <c r="B28" s="30">
         <v>23457.708487240001</v>
       </c>
-      <c r="C28" s="35">
+      <c r="C28" s="30">
         <v>28390.919403627395</v>
       </c>
-      <c r="D28" s="51">
+      <c r="D28" s="46">
         <v>1640.1076464800001</v>
       </c>
-      <c r="E28" s="49">
+      <c r="E28" s="44">
         <v>17.310400000000001</v>
       </c>
-      <c r="F28" s="51"/>
+      <c r="F28" s="46"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="43">
+      <c r="A29" s="38">
         <v>43556</v>
       </c>
-      <c r="B29" s="35">
+      <c r="B29" s="30">
         <v>23305.690210469998</v>
       </c>
-      <c r="C29" s="35">
+      <c r="C29" s="30">
         <v>30010.949539558318</v>
       </c>
-      <c r="D29" s="51">
+      <c r="D29" s="46">
         <v>1677.3577582779999</v>
       </c>
-      <c r="E29" s="49">
+      <c r="E29" s="44">
         <v>17.8918</v>
       </c>
-      <c r="F29" s="51"/>
+      <c r="F29" s="46"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="43">
+      <c r="A30" s="38">
         <v>43586</v>
       </c>
-      <c r="B30" s="35">
+      <c r="B30" s="30">
         <v>23387.52</v>
       </c>
-      <c r="C30" s="35">
+      <c r="C30" s="30">
         <v>30572.302739999999</v>
       </c>
-      <c r="D30" s="51">
+      <c r="D30" s="46">
         <v>1681.09</v>
       </c>
-      <c r="E30" s="49">
+      <c r="E30" s="44">
         <v>18.186</v>
       </c>
-      <c r="F30" s="51"/>
+      <c r="F30" s="46"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="43">
+      <c r="A31" s="38">
         <v>43617</v>
       </c>
-      <c r="B31" s="35">
+      <c r="B31" s="30">
         <v>23430.06766457</v>
       </c>
-      <c r="C31" s="35">
+      <c r="C31" s="30">
         <v>30950.811996</v>
       </c>
-      <c r="D31" s="51">
+      <c r="D31" s="46">
         <v>1705.73</v>
       </c>
-      <c r="E31" s="49">
+      <c r="E31" s="44">
         <v>18.145199999999999</v>
       </c>
-      <c r="F31" s="51"/>
+      <c r="F31" s="46"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="43">
+      <c r="A32" s="38">
         <v>43647</v>
       </c>
-      <c r="B32" s="35">
+      <c r="B32" s="30">
         <v>23243.517859619998</v>
       </c>
-      <c r="C32" s="35">
+      <c r="C32" s="30">
         <v>29870.512989773328</v>
       </c>
-      <c r="D32" s="51">
+      <c r="D32" s="46">
         <v>1684.117192121</v>
       </c>
-      <c r="E32" s="49">
+      <c r="E32" s="44">
         <v>17.736599999999999</v>
       </c>
-      <c r="F32" s="51"/>
+      <c r="F32" s="46"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="43">
+      <c r="A33" s="38">
         <v>43678</v>
       </c>
-      <c r="B33" s="35">
+      <c r="B33" s="30">
         <v>23105.876784029999</v>
       </c>
-      <c r="C33" s="35">
+      <c r="C33" s="30">
         <v>29320.122573580571</v>
       </c>
-      <c r="D33" s="51">
+      <c r="D33" s="46">
         <v>1644.223515527</v>
       </c>
-      <c r="E33" s="49">
+      <c r="E33" s="44">
         <v>17.8322</v>
       </c>
-      <c r="F33" s="51"/>
+      <c r="F33" s="46"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="43">
+      <c r="A34" s="38">
         <v>43709</v>
       </c>
-      <c r="B34" s="35">
+      <c r="B34" s="30">
         <v>23081.774000000001</v>
       </c>
-      <c r="C34" s="35">
+      <c r="C34" s="30">
         <v>29287.832859000002</v>
       </c>
-      <c r="D34" s="51">
+      <c r="D34" s="46">
         <v>1651.5540000000001</v>
       </c>
-      <c r="E34" s="49">
+      <c r="E34" s="44">
         <v>17.733499999999999</v>
       </c>
-      <c r="F34" s="51"/>
+      <c r="F34" s="46"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="43">
+      <c r="A35" s="38">
         <v>43739</v>
       </c>
-      <c r="B35" s="35">
+      <c r="B35" s="30">
         <v>22935.83</v>
       </c>
-      <c r="C35" s="35">
+      <c r="C35" s="30">
         <v>29625.341130000004</v>
       </c>
-      <c r="D35" s="51">
+      <c r="D35" s="46">
         <v>1689.7</v>
       </c>
-      <c r="E35" s="49">
+      <c r="E35" s="44">
         <v>17.532900000000001</v>
       </c>
-      <c r="F35" s="51"/>
+      <c r="F35" s="46"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="43">
+      <c r="A36" s="38">
         <v>43770</v>
       </c>
-      <c r="B36" s="35">
+      <c r="B36" s="30">
         <v>23091.441999999999</v>
       </c>
-      <c r="C36" s="35">
+      <c r="C36" s="30">
         <v>29305.666539577967</v>
       </c>
-      <c r="D36" s="51">
+      <c r="D36" s="46">
         <v>1679.9276876270001</v>
       </c>
-      <c r="E36" s="49">
+      <c r="E36" s="44">
         <v>17.444600000000001</v>
       </c>
-      <c r="F36" s="51"/>
+      <c r="F36" s="46"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="43">
+      <c r="A37" s="38">
         <v>43800</v>
       </c>
-      <c r="B37" s="38">
+      <c r="B37" s="33">
         <v>23168.216431109999</v>
       </c>
-      <c r="C37" s="38">
+      <c r="C37" s="33">
         <v>29322.385347557745</v>
       </c>
-      <c r="D37" s="51">
+      <c r="D37" s="46">
         <v>1703.8685680159999</v>
       </c>
-      <c r="E37" s="50">
+      <c r="E37" s="45">
         <v>17.209299999999999</v>
       </c>
-      <c r="F37" s="51">
+      <c r="F37" s="46">
         <v>206256.239</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="43">
+      <c r="A38" s="38">
         <v>43831</v>
       </c>
-      <c r="B38" s="36">
+      <c r="B38" s="31">
         <v>23396.655969269999</v>
       </c>
-      <c r="C38" s="36">
+      <c r="C38" s="31">
         <v>29326.120517067415</v>
       </c>
-      <c r="D38" s="51">
+      <c r="D38" s="46">
         <v>1704.0856116790001</v>
       </c>
-      <c r="E38" s="48">
+      <c r="E38" s="43">
         <v>17.209299999999999</v>
       </c>
-      <c r="F38" s="51"/>
+      <c r="F38" s="46"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="43">
+      <c r="A39" s="38">
         <v>43862</v>
       </c>
-      <c r="B39" s="35">
+      <c r="B39" s="30">
         <v>23764.79</v>
       </c>
-      <c r="C39" s="35">
+      <c r="C39" s="30">
         <v>29335.032748869395</v>
       </c>
-      <c r="D39" s="51">
+      <c r="D39" s="46">
         <v>1650.715642187</v>
       </c>
-      <c r="E39" s="49">
+      <c r="E39" s="44">
         <v>17.771100000000001</v>
       </c>
-      <c r="F39" s="51"/>
+      <c r="F39" s="46"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="43">
+      <c r="A40" s="38">
         <v>43891</v>
       </c>
-      <c r="B40" s="35">
+      <c r="B40" s="30">
         <v>23855.309474920003</v>
       </c>
-      <c r="C40" s="35">
+      <c r="C40" s="30">
         <v>30269.757752537913</v>
       </c>
-      <c r="D40" s="51">
+      <c r="D40" s="46">
         <v>1665.8370115150001</v>
       </c>
-      <c r="E40" s="49">
+      <c r="E40" s="44">
         <v>18.1709</v>
       </c>
-      <c r="F40" s="51"/>
+      <c r="F40" s="46"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="43">
+      <c r="A41" s="38">
         <v>43922</v>
       </c>
-      <c r="B41" s="35">
+      <c r="B41" s="30">
         <v>24503.671999999999</v>
       </c>
-      <c r="C41" s="35">
+      <c r="C41" s="30">
         <v>33844.83166525104</v>
       </c>
-      <c r="D41" s="51">
+      <c r="D41" s="46">
         <v>1891.0262641500001</v>
       </c>
-      <c r="E41" s="49">
+      <c r="E41" s="44">
         <v>17.897600000000001</v>
       </c>
-      <c r="F41" s="51"/>
+      <c r="F41" s="46"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="43">
+      <c r="A42" s="38">
         <v>43952</v>
       </c>
-      <c r="B42" s="35">
+      <c r="B42" s="30">
         <v>25839.221000000001</v>
       </c>
-      <c r="C42" s="35">
+      <c r="C42" s="30">
         <v>33547.593168600004</v>
       </c>
-      <c r="D42" s="51">
+      <c r="D42" s="46">
         <v>1903.1179999999999</v>
       </c>
-      <c r="E42" s="49">
+      <c r="E42" s="44">
         <v>17.627700000000001</v>
       </c>
-      <c r="F42" s="51"/>
+      <c r="F42" s="46"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="43">
+      <c r="A43" s="38">
         <v>43983</v>
       </c>
-      <c r="B43" s="35">
+      <c r="B43" s="30">
         <v>26565.73</v>
       </c>
-      <c r="C43" s="35">
+      <c r="C43" s="30">
         <v>33429.606516799999</v>
       </c>
-      <c r="D43" s="51">
+      <c r="D43" s="46">
         <v>1940.4680000000001</v>
       </c>
-      <c r="E43" s="49">
+      <c r="E43" s="44">
         <v>17.227599999999999</v>
       </c>
-      <c r="F43" s="51"/>
+      <c r="F43" s="46"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="43">
+      <c r="A44" s="38">
         <v>44013</v>
       </c>
-      <c r="B44" s="35">
+      <c r="B44" s="30">
         <v>27003.612000000001</v>
       </c>
-      <c r="C44" s="35">
+      <c r="C44" s="30">
         <v>33827.074384899999</v>
       </c>
-      <c r="D44" s="51">
+      <c r="D44" s="46">
         <v>2018.069</v>
       </c>
-      <c r="E44" s="49">
+      <c r="E44" s="44">
         <v>16.7621</v>
       </c>
-      <c r="F44" s="51"/>
+      <c r="F44" s="46"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="43">
+      <c r="A45" s="38">
         <v>44044</v>
       </c>
-      <c r="B45" s="35">
+      <c r="B45" s="30">
         <v>27615.344000000001</v>
       </c>
-      <c r="C45" s="35">
+      <c r="C45" s="30">
         <v>33560.606545299997</v>
       </c>
-      <c r="D45" s="51">
+      <c r="D45" s="46">
         <v>2019.011</v>
       </c>
-      <c r="E45" s="49">
+      <c r="E45" s="44">
         <v>16.622299999999999</v>
       </c>
-      <c r="F45" s="51"/>
+      <c r="F45" s="46"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="43">
+      <c r="A46" s="38">
         <v>44075</v>
       </c>
-      <c r="B46" s="35">
+      <c r="B46" s="30">
         <v>28161.432000000001</v>
       </c>
-      <c r="C46" s="35">
+      <c r="C46" s="30">
         <v>34072.543708500001</v>
       </c>
-      <c r="D46" s="51">
+      <c r="D46" s="46">
         <v>2009.4090000000001</v>
       </c>
-      <c r="E46" s="49">
+      <c r="E46" s="44">
         <v>16.956499999999998</v>
       </c>
-      <c r="F46" s="51"/>
+      <c r="F46" s="46"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="43">
+      <c r="A47" s="38">
         <v>44105</v>
       </c>
-      <c r="B47" s="35">
+      <c r="B47" s="30">
         <v>28577.050999999999</v>
       </c>
-      <c r="C47" s="35">
+      <c r="C47" s="30">
         <v>34731.129959900005</v>
       </c>
-      <c r="D47" s="51">
+      <c r="D47" s="46">
         <v>2038.4870000000001</v>
       </c>
-      <c r="E47" s="49">
+      <c r="E47" s="44">
         <v>17.037700000000001</v>
       </c>
-      <c r="F47" s="51"/>
+      <c r="F47" s="46"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="43">
+      <c r="A48" s="38">
         <v>44136</v>
       </c>
-      <c r="B48" s="35">
+      <c r="B48" s="30">
         <v>29068.100999999999</v>
       </c>
-      <c r="C48" s="35">
+      <c r="C48" s="30">
         <v>36893.357945099997</v>
       </c>
-      <c r="D48" s="51">
+      <c r="D48" s="46">
         <v>2140.1970000000001</v>
       </c>
-      <c r="E48" s="49">
+      <c r="E48" s="44">
         <v>17.238299999999999</v>
       </c>
-      <c r="F48" s="51"/>
+      <c r="F48" s="46"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="43">
+      <c r="A49" s="38">
         <v>44166</v>
       </c>
-      <c r="B49" s="38">
+      <c r="B49" s="33">
         <v>29235.620999999999</v>
       </c>
-      <c r="C49" s="38">
+      <c r="C49" s="33">
         <v>38585.114302800001</v>
       </c>
-      <c r="D49" s="51">
+      <c r="D49" s="46">
         <v>2241.4180000000001</v>
       </c>
-      <c r="E49" s="50">
+      <c r="E49" s="45">
         <v>17.214600000000001</v>
       </c>
-      <c r="F49" s="51">
+      <c r="F49" s="46">
         <v>199733.68399999998</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="43">
+      <c r="A50" s="38">
         <v>44197</v>
       </c>
-      <c r="B50" s="36">
+      <c r="B50" s="31">
         <v>29743.435000000001</v>
       </c>
-      <c r="C50" s="36">
+      <c r="C50" s="31">
         <v>38583.784575999998</v>
       </c>
-      <c r="D50" s="51">
+      <c r="D50" s="46">
         <v>2231.36</v>
       </c>
-      <c r="E50" s="48">
+      <c r="E50" s="43">
         <v>17.291599999999999</v>
       </c>
-      <c r="F50" s="51"/>
+      <c r="F50" s="46"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="43">
+      <c r="A51" s="38">
         <v>44228</v>
       </c>
-      <c r="B51" s="35">
+      <c r="B51" s="30">
         <v>30722.1</v>
       </c>
-      <c r="C51" s="35">
+      <c r="C51" s="30">
         <v>39072.890102399993</v>
       </c>
-      <c r="D51" s="51">
+      <c r="D51" s="46">
         <v>2238.5439999999999</v>
       </c>
-      <c r="E51" s="49">
+      <c r="E51" s="44">
         <v>17.454599999999999</v>
       </c>
-      <c r="F51" s="51"/>
+      <c r="F51" s="46"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="43">
+      <c r="A52" s="38">
         <v>44256</v>
       </c>
-      <c r="B52" s="35">
+      <c r="B52" s="30">
         <v>31509.899000000001</v>
       </c>
-      <c r="C52" s="35">
+      <c r="C52" s="30">
         <v>39415.372939799992</v>
       </c>
-      <c r="D52" s="51">
+      <c r="D52" s="46">
         <v>2188.7579999999998</v>
       </c>
-      <c r="E52" s="49">
+      <c r="E52" s="44">
         <v>18.008099999999999</v>
       </c>
-      <c r="F52" s="51"/>
+      <c r="F52" s="46"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="43">
+      <c r="A53" s="38">
         <v>44287</v>
       </c>
-      <c r="B53" s="35">
+      <c r="B53" s="30">
         <v>31893.173999999999</v>
       </c>
-      <c r="C53" s="35">
+      <c r="C53" s="30">
         <v>40540.508072800003</v>
       </c>
-      <c r="D53" s="51">
+      <c r="D53" s="46">
         <v>2277.6590000000001</v>
       </c>
-      <c r="E53" s="49">
+      <c r="E53" s="44">
         <v>17.799199999999999</v>
       </c>
-      <c r="F53" s="51"/>
+      <c r="F53" s="46"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="43">
+      <c r="A54" s="38">
         <v>44317</v>
       </c>
-      <c r="B54" s="35">
+      <c r="B54" s="30">
         <v>33704.366999999998</v>
       </c>
-      <c r="C54" s="35">
+      <c r="C54" s="30">
         <v>40457.77274</v>
       </c>
-      <c r="D54" s="51">
+      <c r="D54" s="46">
         <v>2296.91</v>
       </c>
-      <c r="E54" s="49">
+      <c r="E54" s="44">
         <v>17.614000000000001</v>
       </c>
-      <c r="F54" s="51"/>
+      <c r="F54" s="46"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="43">
+      <c r="A55" s="38">
         <v>44348</v>
       </c>
-      <c r="B55" s="35">
+      <c r="B55" s="30">
         <v>34312.737000000001</v>
       </c>
-      <c r="C55" s="35">
+      <c r="C55" s="30">
         <v>41265.276819999999</v>
       </c>
-      <c r="D55" s="51">
+      <c r="D55" s="46">
         <v>2295.64</v>
       </c>
-      <c r="E55" s="49">
+      <c r="E55" s="44">
         <v>17.9755</v>
       </c>
-      <c r="F55" s="51"/>
+      <c r="F55" s="46"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="43">
+      <c r="A56" s="38">
         <v>44378</v>
       </c>
-      <c r="B56" s="35">
+      <c r="B56" s="30">
         <v>34333.642999999996</v>
       </c>
-      <c r="C56" s="35">
+      <c r="C56" s="30">
         <v>41152.126400000001</v>
       </c>
-      <c r="D56" s="51">
+      <c r="D56" s="46">
         <v>2296</v>
       </c>
-      <c r="E56" s="49">
+      <c r="E56" s="44">
         <v>17.923400000000001</v>
       </c>
-      <c r="F56" s="51"/>
+      <c r="F56" s="46"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="43">
+      <c r="A57" s="38">
         <v>44409</v>
       </c>
-      <c r="B57" s="35">
+      <c r="B57" s="30">
         <v>33317.775999999998</v>
       </c>
-      <c r="C57" s="35">
+      <c r="C57" s="30">
         <v>40150.635200000004</v>
       </c>
-      <c r="D57" s="51">
+      <c r="D57" s="46">
         <v>2268.5</v>
       </c>
-      <c r="E57" s="49">
+      <c r="E57" s="44">
         <v>17.699200000000001</v>
       </c>
-      <c r="F57" s="51"/>
+      <c r="F57" s="46"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="43">
+      <c r="A58" s="38">
         <v>44440</v>
       </c>
-      <c r="B58" s="35">
+      <c r="B58" s="30">
         <v>32857.444000000003</v>
       </c>
-      <c r="C58" s="35">
+      <c r="C58" s="30">
         <v>39537.247442</v>
       </c>
-      <c r="D58" s="51">
+      <c r="D58" s="46">
         <v>2238.46</v>
       </c>
-      <c r="E58" s="49">
+      <c r="E58" s="44">
         <v>17.662700000000001</v>
       </c>
-      <c r="F58" s="51"/>
+      <c r="F58" s="46"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="43">
+      <c r="A59" s="38">
         <v>44470</v>
       </c>
-      <c r="B59" s="35">
+      <c r="B59" s="30">
         <v>33102.642</v>
       </c>
-      <c r="C59" s="35">
+      <c r="C59" s="30">
         <v>40192.533948000004</v>
       </c>
-      <c r="D59" s="51">
+      <c r="D59" s="46">
         <v>2294.5700000000002</v>
       </c>
-      <c r="E59" s="49">
+      <c r="E59" s="44">
         <v>17.516400000000001</v>
       </c>
-      <c r="F59" s="51"/>
+      <c r="F59" s="46"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="43">
+      <c r="A60" s="38">
         <v>44501</v>
       </c>
-      <c r="B60" s="35">
+      <c r="B60" s="30">
         <v>33471.048000000003</v>
       </c>
-      <c r="C60" s="35">
+      <c r="C60" s="30">
         <v>44246.935560000005</v>
       </c>
-      <c r="D60" s="51">
+      <c r="D60" s="46">
         <v>2495.4</v>
       </c>
-      <c r="E60" s="49">
+      <c r="E60" s="44">
         <v>17.731400000000001</v>
       </c>
-      <c r="F60" s="51"/>
+      <c r="F60" s="46"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="43">
+      <c r="A61" s="38">
         <v>44531</v>
       </c>
-      <c r="B61" s="38">
+      <c r="B61" s="33">
         <v>33281.381999999998</v>
       </c>
-      <c r="C61" s="38">
+      <c r="C61" s="33">
         <v>44471.245719999999</v>
       </c>
-      <c r="D61" s="51">
+      <c r="D61" s="46">
         <v>2506.1</v>
       </c>
-      <c r="E61" s="50">
+      <c r="E61" s="45">
         <v>17.745200000000001</v>
       </c>
-      <c r="F61" s="51">
+      <c r="F61" s="46">
         <v>242078.62899999999</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="44">
+      <c r="A62" s="39">
         <v>44562</v>
       </c>
-      <c r="B62" s="36">
+      <c r="B62" s="31">
         <v>33393.214</v>
       </c>
-      <c r="C62" s="36">
+      <c r="C62" s="31">
         <v>45809.800657</v>
       </c>
-      <c r="D62" s="51">
+      <c r="D62" s="46">
         <v>2555.11</v>
       </c>
-      <c r="E62" s="48">
+      <c r="E62" s="43">
         <v>17.928699999999999</v>
       </c>
-      <c r="F62" s="51"/>
+      <c r="F62" s="46"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="43">
+      <c r="A63" s="38">
         <v>44593</v>
       </c>
-      <c r="B63" s="35">
+      <c r="B63" s="30">
         <v>33061.669000000002</v>
       </c>
-      <c r="C63" s="35">
+      <c r="C63" s="30">
         <v>46650.070540000001</v>
       </c>
-      <c r="D63" s="51">
+      <c r="D63" s="46">
         <v>2565.6999999999998</v>
       </c>
-      <c r="E63" s="49">
+      <c r="E63" s="44">
         <v>18.182200000000002</v>
       </c>
-      <c r="F63" s="51"/>
+      <c r="F63" s="46"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="43">
+      <c r="A64" s="38">
         <v>44621</v>
       </c>
-      <c r="B64" s="35">
+      <c r="B64" s="30">
         <v>32196.113000000001</v>
       </c>
-      <c r="C64" s="35">
+      <c r="C64" s="30">
         <v>46565.026112</v>
       </c>
-      <c r="D64" s="51">
+      <c r="D64" s="46">
         <v>2541.44</v>
       </c>
-      <c r="E64" s="49">
+      <c r="E64" s="44">
         <v>18.322299999999998</v>
       </c>
-      <c r="F64" s="51"/>
+      <c r="F64" s="46"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="43">
+      <c r="A65" s="38">
         <v>44652</v>
       </c>
-      <c r="B65" s="35">
+      <c r="B65" s="30">
         <v>32032.978999999999</v>
       </c>
-      <c r="C65" s="35">
+      <c r="C65" s="30">
         <v>45141.912764999994</v>
       </c>
-      <c r="D65" s="51">
+      <c r="D65" s="46">
         <v>2435.4299999999998</v>
       </c>
-      <c r="E65" s="49">
+      <c r="E65" s="44">
         <v>18.535499999999999</v>
       </c>
-      <c r="F65" s="51"/>
+      <c r="F65" s="46"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="43">
+      <c r="A66" s="38">
         <v>44682</v>
       </c>
-      <c r="B66" s="35">
+      <c r="B66" s="30">
         <v>31969.17</v>
       </c>
-      <c r="C66" s="35">
+      <c r="C66" s="30">
         <v>47212.341709999993</v>
       </c>
-      <c r="D66" s="51">
+      <c r="D66" s="46">
         <v>2475.6999999999998</v>
       </c>
-      <c r="E66" s="49">
+      <c r="E66" s="44">
         <v>19.0703</v>
       </c>
-      <c r="F66" s="51"/>
+      <c r="F66" s="46"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="43">
+      <c r="A67" s="38">
         <v>44713</v>
       </c>
-      <c r="B67" s="35">
+      <c r="B67" s="30">
         <v>32220.536</v>
       </c>
-      <c r="C67" s="35">
+      <c r="C67" s="30">
         <v>46671.810064000005</v>
       </c>
-      <c r="D67" s="51">
+      <c r="D67" s="46">
         <v>2440.79</v>
       </c>
-      <c r="E67" s="49">
+      <c r="E67" s="44">
         <v>19.121600000000001</v>
       </c>
-      <c r="F67" s="51"/>
+      <c r="F67" s="46"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="43">
+      <c r="A68" s="38">
         <v>44743</v>
       </c>
-      <c r="B68" s="35">
+      <c r="B68" s="30">
         <v>32049.241000000002</v>
       </c>
-      <c r="C68" s="35">
+      <c r="C68" s="30">
         <v>49361.238166000003</v>
       </c>
-      <c r="D68" s="51">
+      <c r="D68" s="46">
         <v>2553.37</v>
       </c>
-      <c r="E68" s="49">
+      <c r="E68" s="44">
         <v>19.331800000000001</v>
       </c>
-      <c r="F68" s="51"/>
+      <c r="F68" s="46"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="43">
+      <c r="A69" s="38">
         <v>44774</v>
       </c>
-      <c r="B69" s="35">
+      <c r="B69" s="30">
         <v>32662.046999999999</v>
       </c>
-      <c r="C69" s="35">
+      <c r="C69" s="30">
         <v>52768.520168000003</v>
       </c>
-      <c r="D69" s="51">
+      <c r="D69" s="46">
         <v>2725.52</v>
       </c>
-      <c r="E69" s="49">
+      <c r="E69" s="44">
         <v>19.360900000000001</v>
       </c>
-      <c r="F69" s="51"/>
+      <c r="F69" s="46"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="43">
+      <c r="A70" s="38">
         <v>44805</v>
       </c>
-      <c r="B70" s="35">
+      <c r="B70" s="30">
         <v>32962.462</v>
       </c>
-      <c r="C70" s="35">
+      <c r="C70" s="30">
         <v>52537.983680000005</v>
       </c>
-      <c r="D70" s="51">
+      <c r="D70" s="46">
         <v>2687.09</v>
       </c>
-      <c r="E70" s="49">
+      <c r="E70" s="44">
         <v>19.552</v>
       </c>
-      <c r="F70" s="51"/>
+      <c r="F70" s="46"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="43">
+      <c r="A71" s="38">
         <v>44835</v>
       </c>
-      <c r="B71" s="35">
+      <c r="B71" s="30">
         <v>33176.964</v>
       </c>
-      <c r="C71" s="35">
+      <c r="C71" s="30">
         <v>53407.735090000002</v>
       </c>
-      <c r="D71" s="51">
+      <c r="D71" s="46">
         <v>2763.02</v>
       </c>
-      <c r="E71" s="49">
+      <c r="E71" s="44">
         <v>19.329499999999999</v>
       </c>
-      <c r="F71" s="51"/>
+      <c r="F71" s="46"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="43">
+      <c r="A72" s="38">
         <v>44866</v>
       </c>
-      <c r="B72" s="35">
+      <c r="B72" s="30">
         <v>33235.209000000003</v>
       </c>
-      <c r="C72" s="35">
+      <c r="C72" s="30">
         <v>57526.05</v>
       </c>
-      <c r="D72" s="51">
+      <c r="D72" s="46">
         <v>2969.29</v>
       </c>
-      <c r="E72" s="49">
+      <c r="E72" s="44">
         <v>19.373699999999999</v>
       </c>
-      <c r="F72" s="51"/>
+      <c r="F72" s="46"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="43">
+      <c r="A73" s="38">
         <v>44896</v>
       </c>
-      <c r="B73" s="38">
+      <c r="B73" s="33">
         <v>34492.400000000001</v>
       </c>
-      <c r="C73" s="38">
+      <c r="C73" s="33">
         <v>60167.7</v>
       </c>
-      <c r="D73" s="51">
+      <c r="D73" s="46">
         <v>3140.6</v>
       </c>
-      <c r="E73" s="50">
+      <c r="E73" s="45">
         <v>19.157900000000001</v>
       </c>
-      <c r="F73" s="51">
+      <c r="F73" s="46">
         <v>274207.49935022759</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74" s="44">
+      <c r="A74" s="39">
         <v>44927</v>
       </c>
-      <c r="B74" s="36">
+      <c r="B74" s="31">
         <v>35081.385999999999</v>
       </c>
-      <c r="C74" s="36">
+      <c r="C74" s="31">
         <v>63196.23</v>
       </c>
-      <c r="D74" s="51">
+      <c r="D74" s="46">
         <v>3368.2</v>
       </c>
-      <c r="E74" s="48">
+      <c r="E74" s="43">
         <v>18.762499999999999</v>
       </c>
-      <c r="F74" s="51"/>
+      <c r="F74" s="46"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" s="43">
+      <c r="A75" s="38">
         <v>44958</v>
       </c>
-      <c r="B75" s="35">
+      <c r="B75" s="30">
         <v>35086.69</v>
       </c>
-      <c r="C75" s="35">
+      <c r="C75" s="30">
         <v>61909.59</v>
       </c>
-      <c r="D75" s="51">
+      <c r="D75" s="46">
         <v>3279.4</v>
       </c>
-      <c r="E75" s="49">
+      <c r="E75" s="44">
         <v>18.878499999999999</v>
       </c>
-      <c r="F75" s="51"/>
+      <c r="F75" s="46"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" s="43">
+      <c r="A76" s="38">
         <v>44986</v>
       </c>
-      <c r="B76" s="35">
+      <c r="B76" s="30">
         <v>34875.120000000003</v>
       </c>
-      <c r="C76" s="35">
+      <c r="C76" s="30">
         <v>61712.119999999995</v>
       </c>
-      <c r="D76" s="51">
+      <c r="D76" s="46">
         <v>3352.86</v>
       </c>
-      <c r="E76" s="49">
+      <c r="E76" s="44">
         <v>18.405799999999999</v>
       </c>
-      <c r="F76" s="51"/>
+      <c r="F76" s="46"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" s="43">
+      <c r="A77" s="38">
         <v>45017</v>
       </c>
-      <c r="B77" s="35">
+      <c r="B77" s="30">
         <v>36341.599999999999</v>
       </c>
-      <c r="C77" s="35">
+      <c r="C77" s="30">
         <v>62689.9</v>
       </c>
-      <c r="D77" s="51">
+      <c r="D77" s="46">
         <v>3479.8</v>
       </c>
-      <c r="E77" s="49">
+      <c r="E77" s="44">
         <v>18.015499999999999</v>
       </c>
-      <c r="F77" s="51"/>
+      <c r="F77" s="46"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" s="43">
+      <c r="A78" s="38">
         <v>45047</v>
       </c>
-      <c r="B78" s="35">
+      <c r="B78" s="30">
         <v>36518.300000000003</v>
       </c>
-      <c r="C78" s="35">
+      <c r="C78" s="30">
         <v>60971.97</v>
       </c>
-      <c r="D78" s="51">
+      <c r="D78" s="46">
         <v>3426.57</v>
       </c>
-      <c r="E78" s="49">
+      <c r="E78" s="44">
         <v>17.793900000000001</v>
       </c>
-      <c r="F78" s="51"/>
+      <c r="F78" s="46"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79" s="43">
+      <c r="A79" s="38">
         <v>45078</v>
       </c>
-      <c r="B79" s="35">
+      <c r="B79" s="30">
         <v>36812.080000000002</v>
       </c>
-      <c r="C79" s="35">
+      <c r="C79" s="30">
         <v>63124.88</v>
       </c>
-      <c r="D79" s="51">
+      <c r="D79" s="46">
         <v>3453.71</v>
       </c>
-      <c r="E79" s="49">
+      <c r="E79" s="44">
         <v>18.2774</v>
       </c>
-      <c r="F79" s="51"/>
+      <c r="F79" s="46"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A80" s="43">
+      <c r="A80" s="38">
         <v>45108</v>
       </c>
-      <c r="B80" s="35">
+      <c r="B80" s="30">
         <v>38602.5</v>
       </c>
-      <c r="C80" s="35">
+      <c r="C80" s="30">
         <v>62568.92</v>
       </c>
-      <c r="D80" s="51">
+      <c r="D80" s="46">
         <v>3497.17</v>
       </c>
-      <c r="E80" s="49">
+      <c r="E80" s="44">
         <v>17.891300000000001</v>
       </c>
-      <c r="F80" s="51"/>
+      <c r="F80" s="46"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A81" s="43">
+      <c r="A81" s="38">
         <v>45139</v>
       </c>
-      <c r="B81" s="35">
+      <c r="B81" s="30">
         <v>38952.69</v>
       </c>
-      <c r="C81" s="35">
+      <c r="C81" s="30">
         <v>57788.27</v>
       </c>
-      <c r="D81" s="51">
+      <c r="D81" s="46">
         <v>3233.96</v>
       </c>
-      <c r="E81" s="49">
+      <c r="E81" s="44">
         <v>17.869199999999999</v>
       </c>
-      <c r="F81" s="51"/>
+      <c r="F81" s="46"/>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82" s="43">
+      <c r="A82" s="38">
         <v>45170</v>
       </c>
-      <c r="B82" s="35">
+      <c r="B82" s="30">
         <v>39823.589999999997</v>
       </c>
-      <c r="C82" s="35">
+      <c r="C82" s="30">
         <v>58525.93</v>
       </c>
-      <c r="D82" s="51">
+      <c r="D82" s="46">
         <v>3223.63</v>
       </c>
-      <c r="E82" s="49">
+      <c r="E82" s="44">
         <v>18.1553</v>
       </c>
-      <c r="F82" s="51"/>
+      <c r="F82" s="46"/>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A83" s="43">
+      <c r="A83" s="38">
         <v>45200</v>
       </c>
-      <c r="B83" s="35">
+      <c r="B83" s="30">
         <v>39194.53</v>
       </c>
-      <c r="C83" s="35">
+      <c r="C83" s="30">
         <v>61997.69</v>
       </c>
-      <c r="D83" s="51">
+      <c r="D83" s="46">
         <v>3414.91</v>
       </c>
-      <c r="E83" s="49">
+      <c r="E83" s="44">
         <v>18.155000000000001</v>
       </c>
-      <c r="F83" s="51"/>
+      <c r="F83" s="46"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A84" s="43">
+      <c r="A84" s="38">
         <v>45231</v>
       </c>
-      <c r="B84" s="35">
+      <c r="B84" s="30">
         <v>38968.089999999997</v>
       </c>
-      <c r="C84" s="35">
+      <c r="C84" s="30">
         <v>62552.6</v>
       </c>
-      <c r="D84" s="51">
+      <c r="D84" s="46">
         <v>3505.6</v>
       </c>
-      <c r="E84" s="49">
+      <c r="E84" s="44">
         <v>17.843499999999999</v>
       </c>
-      <c r="F84" s="51"/>
+      <c r="F84" s="46"/>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85" s="43">
+      <c r="A85" s="38">
         <v>45261</v>
       </c>
-      <c r="B85" s="38">
+      <c r="B85" s="33">
         <v>39666.120000000003</v>
       </c>
-      <c r="C85" s="38">
+      <c r="C85" s="33">
         <v>64336.99</v>
       </c>
-      <c r="D85" s="51">
+      <c r="D85" s="46">
         <v>3696.21</v>
       </c>
-      <c r="E85" s="50">
+      <c r="E85" s="45">
         <v>17.406199999999998</v>
       </c>
-      <c r="F85" s="51">
+      <c r="F85" s="46">
         <v>303554</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A86" s="44">
+      <c r="A86" s="39">
         <v>45292</v>
       </c>
-      <c r="B86" s="36">
+      <c r="B86" s="31">
         <v>39855.519999999997</v>
       </c>
-      <c r="C86" s="36">
+      <c r="C86" s="31">
         <v>63951.15</v>
       </c>
-      <c r="D86" s="51">
+      <c r="D86" s="46">
         <v>3605.01</v>
       </c>
-      <c r="E86" s="48">
+      <c r="E86" s="43">
         <v>17.7395</v>
       </c>
-      <c r="F86" s="51"/>
+      <c r="F86" s="46"/>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A87" s="43">
+      <c r="A87" s="38">
         <v>45323</v>
       </c>
-      <c r="B87" s="35">
+      <c r="B87" s="30">
         <v>40546.71</v>
       </c>
-      <c r="C87" s="35">
+      <c r="C87" s="30">
         <v>64545.1</v>
       </c>
-      <c r="D87" s="51">
+      <c r="D87" s="46">
         <v>3620.535689244145</v>
       </c>
-      <c r="E87" s="49">
+      <c r="E87" s="44">
         <v>17.827500000000001</v>
       </c>
-      <c r="F87" s="51"/>
+      <c r="F87" s="46"/>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A88" s="43">
+      <c r="A88" s="38">
         <v>45352</v>
       </c>
-      <c r="B88" s="35">
+      <c r="B88" s="30">
         <v>42110.400000000001</v>
       </c>
-      <c r="C88" s="35">
+      <c r="C88" s="30">
         <v>63689.36</v>
       </c>
-      <c r="D88" s="51">
+      <c r="D88" s="46">
         <v>3609.51</v>
       </c>
-      <c r="E88" s="49">
+      <c r="E88" s="44">
         <v>17.6449</v>
       </c>
-      <c r="F88" s="51"/>
+      <c r="F88" s="46"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A89" s="43">
+      <c r="A89" s="38">
         <v>45383</v>
       </c>
-      <c r="B89" s="35">
+      <c r="B89" s="30">
         <v>42491.64</v>
       </c>
-      <c r="C89" s="35">
+      <c r="C89" s="30">
         <v>63687.55</v>
       </c>
-      <c r="D89" s="51">
+      <c r="D89" s="46">
         <v>3574.6</v>
       </c>
-      <c r="E89" s="49">
+      <c r="E89" s="44">
         <v>17.816700000000001</v>
       </c>
-      <c r="F89" s="51"/>
+      <c r="F89" s="46"/>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A90" s="43">
+      <c r="A90" s="38">
         <v>45413</v>
       </c>
-      <c r="B90" s="35">
+      <c r="B90" s="30">
         <v>41716.85</v>
       </c>
-      <c r="C90" s="35">
+      <c r="C90" s="30">
         <v>62871.91</v>
       </c>
-      <c r="D90" s="51">
+      <c r="D90" s="46">
         <v>3552.51</v>
       </c>
-      <c r="E90" s="49">
+      <c r="E90" s="44">
         <v>17.697900000000001</v>
       </c>
-      <c r="F90" s="51"/>
+      <c r="F90" s="46"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A91" s="43">
+      <c r="A91" s="38">
         <v>45444</v>
       </c>
-      <c r="B91" s="35">
+      <c r="B91" s="30">
         <v>43812.959999999999</v>
       </c>
-      <c r="C91" s="35">
+      <c r="C91" s="30">
         <v>63227.4</v>
       </c>
-      <c r="D91" s="51">
+      <c r="D91" s="46">
         <v>3526.6</v>
       </c>
-      <c r="E91" s="49">
+      <c r="E91" s="44">
         <v>17.928699999999999</v>
       </c>
-      <c r="F91" s="51"/>
+      <c r="F91" s="46"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A92" s="43">
+      <c r="A92" s="38">
         <v>45474</v>
       </c>
-      <c r="B92" s="35">
+      <c r="B92" s="30">
         <v>43916.800000000003</v>
       </c>
-      <c r="C92" s="35">
+      <c r="C92" s="30">
         <v>65807.740000000005</v>
       </c>
-      <c r="D92" s="51">
+      <c r="D92" s="46">
         <v>3712.06</v>
       </c>
-      <c r="E92" s="49">
+      <c r="E92" s="44">
         <v>17.728100000000001</v>
       </c>
-      <c r="F92" s="51"/>
+      <c r="F92" s="46"/>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A93" s="43">
+      <c r="A93" s="38">
         <v>45505</v>
       </c>
-      <c r="B93" s="35">
+      <c r="B93" s="30">
         <v>42476.62</v>
       </c>
-      <c r="C93" s="35">
+      <c r="C93" s="30">
         <v>66338.149999999994</v>
       </c>
-      <c r="D93" s="51">
+      <c r="D93" s="46">
         <v>3812.65</v>
       </c>
-      <c r="E93" s="49">
+      <c r="E93" s="44">
         <v>17.3995</v>
       </c>
-      <c r="F93" s="51"/>
+      <c r="F93" s="46"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A94" s="43">
+      <c r="A94" s="38">
         <v>45536</v>
       </c>
-      <c r="B94" s="35">
+      <c r="B94" s="30">
         <v>42373.52</v>
       </c>
-      <c r="C94" s="35">
+      <c r="C94" s="30">
         <v>67552.47</v>
       </c>
-      <c r="D94" s="51">
+      <c r="D94" s="46">
         <v>3876.76</v>
       </c>
-      <c r="E94" s="49">
+      <c r="E94" s="44">
         <v>17.425000000000001</v>
       </c>
-      <c r="F94" s="51"/>
+      <c r="F94" s="46"/>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A95" s="43">
+      <c r="A95" s="38">
         <v>45566</v>
       </c>
-      <c r="B95" s="35">
+      <c r="B95" s="30">
         <v>41007.089999999997</v>
       </c>
-      <c r="C95" s="35">
+      <c r="C95" s="30">
         <v>68498.789999999994</v>
       </c>
-      <c r="D95" s="51">
+      <c r="D95" s="46">
         <v>3821.47</v>
       </c>
-      <c r="E95" s="49">
+      <c r="E95" s="44">
         <v>17.924700000000001</v>
       </c>
-      <c r="F95" s="51"/>
+      <c r="F95" s="46"/>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A96" s="43">
+      <c r="A96" s="38">
         <v>45597</v>
       </c>
-      <c r="B96" s="35">
+      <c r="B96" s="30">
         <v>42865.15</v>
       </c>
-      <c r="C96" s="35">
+      <c r="C96" s="30">
         <v>68738.490000000005</v>
       </c>
-      <c r="D96" s="51">
+      <c r="D96" s="46">
         <v>3759.02</v>
       </c>
-      <c r="E96" s="49">
+      <c r="E96" s="44">
         <v>18.286300000000001</v>
       </c>
-      <c r="F96" s="51"/>
+      <c r="F96" s="46"/>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A97" s="43">
+      <c r="A97" s="38">
         <v>45627</v>
       </c>
-      <c r="B97" s="38">
+      <c r="B97" s="33">
         <v>43961.18</v>
       </c>
-      <c r="C97" s="38">
+      <c r="C97" s="33">
         <v>77434.399999999994</v>
       </c>
-      <c r="D97" s="51">
+      <c r="D97" s="46">
         <v>4190.38</v>
       </c>
-      <c r="E97" s="50">
+      <c r="E97" s="45">
         <v>18.479099999999999</v>
       </c>
-      <c r="F97" s="51">
+      <c r="F97" s="46">
         <v>323816.82400000002</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A98" s="44">
+      <c r="A98" s="39">
         <v>45658</v>
       </c>
-      <c r="B98" s="36">
+      <c r="B98" s="31">
         <v>44328.3</v>
       </c>
-      <c r="C98" s="36">
+      <c r="C98" s="31">
         <v>77867.497187012137</v>
       </c>
-      <c r="D98" s="51">
+      <c r="D98" s="46">
         <v>4169.2990719310001</v>
       </c>
-      <c r="E98" s="48">
+      <c r="E98" s="43">
         <v>18.676400000000001</v>
       </c>
-      <c r="F98" s="51"/>
+      <c r="F98" s="46"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A99" s="43">
+      <c r="A99" s="38">
         <v>45689</v>
       </c>
-      <c r="B99" s="35">
+      <c r="B99" s="30">
         <v>45298.53</v>
       </c>
-      <c r="C99" s="35">
+      <c r="C99" s="30">
         <v>78324.028756999978</v>
       </c>
-      <c r="D99" s="51">
+      <c r="D99" s="46">
         <v>4201.7299999999996</v>
       </c>
-      <c r="E99" s="49">
+      <c r="E99" s="44">
         <v>18.640899999999998</v>
       </c>
-      <c r="F99" s="51"/>
+      <c r="F99" s="46"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A100" s="43">
+      <c r="A100" s="38">
         <v>45717</v>
       </c>
-      <c r="B100" s="35">
+      <c r="B100" s="30">
         <v>46748.69</v>
       </c>
-      <c r="C100" s="35">
+      <c r="C100" s="30">
         <v>76219.363899000004</v>
       </c>
-      <c r="D100" s="51">
+      <c r="D100" s="46">
         <v>4222.8900000000003</v>
       </c>
-      <c r="E100" s="49">
+      <c r="E100" s="44">
         <v>18.049099999999999</v>
       </c>
-      <c r="F100" s="51"/>
+      <c r="F100" s="46"/>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A101" s="43">
+      <c r="A101" s="38">
         <v>45748</v>
       </c>
-      <c r="B101" s="35">
+      <c r="B101" s="30">
         <v>48088.29</v>
       </c>
-      <c r="C101" s="35">
+      <c r="C101" s="30">
         <v>74915.818013999989</v>
       </c>
-      <c r="D101" s="51">
+      <c r="D101" s="46">
         <v>4354.71</v>
       </c>
-      <c r="E101" s="49">
+      <c r="E101" s="44">
         <v>17.203399999999998</v>
       </c>
-      <c r="F101" s="51"/>
+      <c r="F101" s="46"/>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A102" s="43">
+      <c r="A102" s="38">
         <v>45778</v>
       </c>
-      <c r="B102" s="35">
+      <c r="B102" s="30">
         <v>48778.86</v>
       </c>
-      <c r="C102" s="35">
+      <c r="C102" s="30">
         <v>73322.864999999991</v>
       </c>
-      <c r="D102" s="51">
+      <c r="D102" s="46">
         <v>4232.2</v>
       </c>
-      <c r="E102" s="49">
+      <c r="E102" s="44">
         <v>17.324999999999999</v>
       </c>
-      <c r="F102" s="51"/>
+      <c r="F102" s="46"/>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A103" s="43">
+      <c r="A103" s="38">
         <v>45809</v>
       </c>
-      <c r="B103" s="35">
+      <c r="B103" s="30">
         <v>48478.44</v>
       </c>
-      <c r="C103" s="35">
+      <c r="C103" s="30">
         <v>78698</v>
       </c>
-      <c r="D103" s="51">
+      <c r="D103" s="46">
         <v>4671.49</v>
       </c>
-      <c r="E103" s="49">
+      <c r="E103" s="44">
         <v>16.847200000000001</v>
       </c>
-      <c r="F103" s="51"/>
+      <c r="F103" s="46"/>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A104" s="43">
+      <c r="A104" s="38">
         <v>45839</v>
       </c>
-      <c r="B104" s="35">
+      <c r="B104" s="30">
         <v>46204.65</v>
       </c>
-      <c r="C104" s="35">
+      <c r="C104" s="30">
         <v>78021.8</v>
       </c>
-      <c r="D104" s="51">
+      <c r="D104" s="46">
         <v>4561.45</v>
       </c>
-      <c r="E104" s="49">
+      <c r="E104" s="44">
         <v>17.100000000000001</v>
       </c>
-      <c r="F104" s="51"/>
+      <c r="F104" s="46"/>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A105" s="43">
+      <c r="A105" s="38">
         <v>45870</v>
       </c>
-      <c r="B105" s="35">
+      <c r="B105" s="30">
         <v>47357.19</v>
       </c>
-      <c r="C105" s="35">
+      <c r="C105" s="30">
         <v>78384.240000000005</v>
       </c>
-      <c r="D105" s="51">
+      <c r="D105" s="46">
         <v>4711.16</v>
       </c>
-      <c r="E105" s="49">
+      <c r="E105" s="44">
         <v>16.399999999999999</v>
       </c>
-      <c r="F105" s="51"/>
+      <c r="F105" s="46"/>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A106" s="38">
+        <v>45901</v>
+      </c>
+      <c r="B106" s="30">
+        <v>47859.54</v>
+      </c>
+      <c r="C106" s="30">
+        <v>79413.3</v>
+      </c>
+      <c r="D106" s="46">
+        <v>4746.1400000000003</v>
+      </c>
+      <c r="E106" s="44">
+        <v>16.73</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A107" s="38">
+        <v>45931</v>
+      </c>
+      <c r="B107" s="30">
+        <v>48674.45</v>
+      </c>
+      <c r="C107" s="30">
+        <v>79974.460000000006</v>
+      </c>
+      <c r="D107" s="46">
+        <v>4696.2299999999996</v>
+      </c>
+      <c r="E107" s="44">
+        <v>17.02</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A108" s="38">
+        <v>45962</v>
+      </c>
+      <c r="B108" s="30">
+        <v>49547.46</v>
+      </c>
+      <c r="C108" s="30">
+        <v>79584.27</v>
+      </c>
+      <c r="D108" s="46">
+        <v>4682.58</v>
+      </c>
+      <c r="E108" s="44">
+        <v>16.989999999999998</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
